--- a/gantt-chart TIMELINE per 2 Maret 2026 rev.xlsx
+++ b/gantt-chart TIMELINE per 2 Maret 2026 rev.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29628"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Lw\GANTT CHART\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9D9865CB-3B24-428C-9E7E-59A2D4ED0616}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760"/>
   </bookViews>
   <sheets>
     <sheet name="GanttChart" sheetId="9" r:id="rId1"/>
@@ -23,7 +17,7 @@
   <definedNames>
     <definedName name="prevWBS" localSheetId="5">etc!$A1048576</definedName>
     <definedName name="prevWBS" localSheetId="0">GanttChart!$A1048576</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">GanttChart!$A$1:$BN$82</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">GanttChart!$A$1:$BN$83</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">GanttChartPro!$A$1:$C$47</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">GanttChart!$4:$7</definedName>
     <definedName name="valuevx">42.314159</definedName>
@@ -31,7 +25,7 @@
     <definedName name="vertex42_id" hidden="1">"gantt-chart_L.xlsx"</definedName>
     <definedName name="vertex42_title" hidden="1">"Gantt Chart Template"</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="144525"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -47,14 +41,14 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>Vertex42</author>
     <author>Vertex42.com Templates</author>
     <author>BC</author>
   </authors>
   <commentList>
-    <comment ref="A7" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
+    <comment ref="A7" authorId="0">
       <text>
         <r>
           <rPr>
@@ -79,7 +73,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B7" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
+    <comment ref="B7" authorId="0">
       <text>
         <r>
           <rPr>
@@ -101,7 +95,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C7" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
+    <comment ref="C7" authorId="0">
       <text>
         <r>
           <rPr>
@@ -123,10 +117,10 @@
         </r>
       </text>
     </comment>
-    <comment ref="D7" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000004000000}">
+    <comment ref="D7" authorId="0">
       <text/>
     </comment>
-    <comment ref="E7" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000005000000}">
+    <comment ref="E7" authorId="0">
       <text>
         <r>
           <rPr>
@@ -237,7 +231,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F7" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000006000000}">
+    <comment ref="F7" authorId="1">
       <text>
         <r>
           <rPr>
@@ -259,7 +253,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G7" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000007000000}">
+    <comment ref="G7" authorId="0">
       <text>
         <r>
           <rPr>
@@ -333,7 +327,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H7" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000008000000}">
+    <comment ref="H7" authorId="0">
       <text>
         <r>
           <rPr>
@@ -355,7 +349,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I7" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000009000000}">
+    <comment ref="I7" authorId="0">
       <text>
         <r>
           <rPr>
@@ -377,7 +371,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B23" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000A000000}">
+    <comment ref="B23" authorId="2">
       <text>
         <r>
           <rPr>
@@ -402,7 +396,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B24" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000B000000}">
+    <comment ref="B24" authorId="2">
       <text>
         <r>
           <rPr>
@@ -502,7 +496,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B25" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000C000000}">
+    <comment ref="B25" authorId="2">
       <text>
         <r>
           <rPr>
@@ -533,7 +527,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B26" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000D000000}">
+    <comment ref="B26" authorId="2">
       <text>
         <r>
           <rPr>
@@ -566,7 +560,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B27" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000E000000}">
+    <comment ref="B27" authorId="2">
       <text>
         <r>
           <rPr>
@@ -657,7 +651,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B28" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000F000000}">
+    <comment ref="B28" authorId="2">
       <text>
         <r>
           <rPr>
@@ -688,7 +682,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B29" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0000-000010000000}">
+    <comment ref="B29" authorId="2">
       <text>
         <r>
           <rPr>
@@ -717,7 +711,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B30" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0000-000011000000}">
+    <comment ref="B30" authorId="2">
       <text>
         <r>
           <rPr>
@@ -737,7 +731,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B31" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0000-000012000000}">
+    <comment ref="B31" authorId="2">
       <text>
         <r>
           <rPr>
@@ -766,7 +760,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B32" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0000-000013000000}">
+    <comment ref="B32" authorId="2">
       <text>
         <r>
           <rPr>
@@ -795,17 +789,51 @@
         </r>
       </text>
     </comment>
+    <comment ref="B45" authorId="2">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>BC:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+$url = "https://my430621-api.s4hana.cloud.sap/sap/opu/odata/sap/API_MATERIAL_STOCK_SRV/A_MatlStkInAcctMod";
+$username = "LEUWITEX_US_SAP_COM_0947";
+$password = "qyUUYn%4be7bl&gt;m(VT/9nuW#3/342j~W9{C/88jL";
+CREATE TABLE pz_material_stock (
+    id SERIAL PRIMARY KEY, -- optional, untuk unique identifier
+    material VARCHAR(100) NOT NULL,
+    plant VARCHAR(10) NOT NULL,
+    storage_location VARCHAR(20),
+    batch VARCHAR(50),
+    inventory_stock_type VARCHAR(5),
+    base_unit VARCHAR(10),
+    warehouse_stock_qty NUMERIC(18,3) DEFAULT 0
+);</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>Vertex42</author>
   </authors>
   <commentList>
-    <comment ref="C16" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000001000000}">
+    <comment ref="C16" authorId="0">
       <text>
         <r>
           <rPr>
@@ -822,7 +850,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="338" uniqueCount="240">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="241">
   <si>
     <t xml:space="preserve">Project Start Date </t>
   </si>
@@ -2298,11 +2326,14 @@
   <si>
     <t>Star</t>
   </si>
+  <si>
+    <t>Buat UI penarikan data dari API dan insert data Material Stock</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="5">
     <numFmt numFmtId="164" formatCode="ddd\ m/dd/yy"/>
     <numFmt numFmtId="165" formatCode="m/d/yyyy\ \(dddd\)"/>
@@ -2881,7 +2912,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="120">
+  <cellXfs count="119">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -3173,6 +3204,28 @@
     <xf numFmtId="0" fontId="1" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="34" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="166" fontId="34" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3186,36 +3239,11 @@
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="34" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -3223,7 +3251,7 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="10">
+  <dxfs count="14">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -3237,6 +3265,16 @@
           <bgColor theme="0" tint="-0.499984740745262"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color rgb="FFC00000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFC00000"/>
+        </right>
+      </border>
     </dxf>
     <dxf>
       <border>
@@ -3305,6 +3343,30 @@
           <bgColor theme="5"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="0" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color rgb="FFC00000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFC00000"/>
+        </right>
+      </border>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -3417,7 +3479,7 @@
         <xdr:cNvPr id="8236" name="Text Box 44" hidden="1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00002C200000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0000-00002C200000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3473,14 +3535,11 @@
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s8238"/>
                 </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00002E200000}"/>
-                </a:ext>
               </a:extLst>
             </xdr:cNvPr>
             <xdr:cNvSpPr/>
           </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
+          <xdr:spPr>
             <a:xfrm>
               <a:off x="0" y="0"/>
               <a:ext cx="0" cy="0"/>
@@ -3488,25 +3547,6 @@
             <a:prstGeom prst="rect">
               <a:avLst/>
             </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:noFill/>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:noFill/>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
           </xdr:spPr>
         </xdr:sp>
         <xdr:clientData fPrintsWithSheet="0"/>
@@ -3537,7 +3577,7 @@
         <xdr:cNvPr id="2" name="Picture 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0100-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3621,7 +3661,7 @@
         <xdr:cNvPr id="4" name="Picture 3">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000004000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0100-000004000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3676,7 +3716,7 @@
         <xdr:cNvPr id="5" name="Picture 4">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000005000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0200-000005000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3731,7 +3771,7 @@
         <xdr:cNvPr id="4" name="Picture 3">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000004000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0300-000004000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3786,7 +3826,7 @@
         <xdr:cNvPr id="12289" name="AutoShape 1" descr="blob:https://web.whatsapp.com/4841a61e-759f-484d-9013-f081556103c8">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0400-000001300000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0400-000001300000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3834,7 +3874,7 @@
         <xdr:cNvPr id="12291" name="AutoShape 3" descr="blob:https://web.whatsapp.com/4841a61e-759f-484d-9013-f081556103c8">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0400-000003300000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0400-000003300000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4153,11 +4193,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet8">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:BN114"/>
+  <dimension ref="A1:BN115"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="6.85546875" customWidth="1"/>
@@ -4182,27 +4222,27 @@
       <c r="E1" s="57"/>
       <c r="F1" s="57"/>
       <c r="I1" s="58"/>
-      <c r="K1" s="113"/>
-      <c r="L1" s="113"/>
-      <c r="M1" s="113"/>
-      <c r="N1" s="113"/>
-      <c r="O1" s="113"/>
-      <c r="P1" s="113"/>
-      <c r="Q1" s="113"/>
-      <c r="R1" s="113"/>
-      <c r="S1" s="113"/>
-      <c r="T1" s="113"/>
-      <c r="U1" s="113"/>
-      <c r="V1" s="113"/>
-      <c r="W1" s="113"/>
-      <c r="X1" s="113"/>
-      <c r="Y1" s="113"/>
-      <c r="Z1" s="113"/>
-      <c r="AA1" s="113"/>
-      <c r="AB1" s="113"/>
-      <c r="AC1" s="113"/>
-      <c r="AD1" s="113"/>
-      <c r="AE1" s="113"/>
+      <c r="K1" s="108"/>
+      <c r="L1" s="108"/>
+      <c r="M1" s="108"/>
+      <c r="N1" s="108"/>
+      <c r="O1" s="108"/>
+      <c r="P1" s="108"/>
+      <c r="Q1" s="108"/>
+      <c r="R1" s="108"/>
+      <c r="S1" s="108"/>
+      <c r="T1" s="108"/>
+      <c r="U1" s="108"/>
+      <c r="V1" s="108"/>
+      <c r="W1" s="108"/>
+      <c r="X1" s="108"/>
+      <c r="Y1" s="108"/>
+      <c r="Z1" s="108"/>
+      <c r="AA1" s="108"/>
+      <c r="AB1" s="108"/>
+      <c r="AC1" s="108"/>
+      <c r="AD1" s="108"/>
+      <c r="AE1" s="108"/>
     </row>
     <row r="2" spans="1:66" ht="18" customHeight="1">
       <c r="A2" s="59"/>
@@ -4239,11 +4279,11 @@
       <c r="B4" s="66" t="s">
         <v>0</v>
       </c>
-      <c r="C4" s="114">
+      <c r="C4" s="109">
         <v>45986</v>
       </c>
-      <c r="D4" s="114"/>
-      <c r="E4" s="114"/>
+      <c r="D4" s="109"/>
+      <c r="E4" s="109"/>
       <c r="F4" s="65"/>
       <c r="G4" s="66" t="s">
         <v>1</v>
@@ -4338,96 +4378,96 @@
       <c r="B5" s="66" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="109" t="s">
+      <c r="C5" s="116" t="s">
         <v>3</v>
       </c>
-      <c r="D5" s="109"/>
-      <c r="E5" s="109"/>
+      <c r="D5" s="116"/>
+      <c r="E5" s="116"/>
       <c r="F5" s="65"/>
       <c r="G5" s="65"/>
       <c r="H5" s="65"/>
       <c r="I5" s="65"/>
       <c r="J5" s="65"/>
-      <c r="K5" s="106">
+      <c r="K5" s="113">
         <f>K6</f>
         <v>45985</v>
       </c>
-      <c r="L5" s="107"/>
-      <c r="M5" s="107"/>
-      <c r="N5" s="107"/>
-      <c r="O5" s="107"/>
-      <c r="P5" s="107"/>
-      <c r="Q5" s="108"/>
-      <c r="R5" s="106">
+      <c r="L5" s="114"/>
+      <c r="M5" s="114"/>
+      <c r="N5" s="114"/>
+      <c r="O5" s="114"/>
+      <c r="P5" s="114"/>
+      <c r="Q5" s="115"/>
+      <c r="R5" s="113">
         <f>R6</f>
         <v>45992</v>
       </c>
-      <c r="S5" s="107"/>
-      <c r="T5" s="107"/>
-      <c r="U5" s="107"/>
-      <c r="V5" s="107"/>
-      <c r="W5" s="107"/>
-      <c r="X5" s="108"/>
-      <c r="Y5" s="106">
+      <c r="S5" s="114"/>
+      <c r="T5" s="114"/>
+      <c r="U5" s="114"/>
+      <c r="V5" s="114"/>
+      <c r="W5" s="114"/>
+      <c r="X5" s="115"/>
+      <c r="Y5" s="113">
         <f>Y6</f>
         <v>45999</v>
       </c>
-      <c r="Z5" s="107"/>
-      <c r="AA5" s="107"/>
-      <c r="AB5" s="107"/>
-      <c r="AC5" s="107"/>
-      <c r="AD5" s="107"/>
-      <c r="AE5" s="108"/>
-      <c r="AF5" s="106">
+      <c r="Z5" s="114"/>
+      <c r="AA5" s="114"/>
+      <c r="AB5" s="114"/>
+      <c r="AC5" s="114"/>
+      <c r="AD5" s="114"/>
+      <c r="AE5" s="115"/>
+      <c r="AF5" s="113">
         <f>AF6</f>
         <v>46006</v>
       </c>
-      <c r="AG5" s="107"/>
-      <c r="AH5" s="107"/>
-      <c r="AI5" s="107"/>
-      <c r="AJ5" s="107"/>
-      <c r="AK5" s="107"/>
-      <c r="AL5" s="108"/>
-      <c r="AM5" s="106">
+      <c r="AG5" s="114"/>
+      <c r="AH5" s="114"/>
+      <c r="AI5" s="114"/>
+      <c r="AJ5" s="114"/>
+      <c r="AK5" s="114"/>
+      <c r="AL5" s="115"/>
+      <c r="AM5" s="113">
         <f>AM6</f>
         <v>46013</v>
       </c>
-      <c r="AN5" s="107"/>
-      <c r="AO5" s="107"/>
-      <c r="AP5" s="107"/>
-      <c r="AQ5" s="107"/>
-      <c r="AR5" s="107"/>
-      <c r="AS5" s="108"/>
-      <c r="AT5" s="106">
+      <c r="AN5" s="114"/>
+      <c r="AO5" s="114"/>
+      <c r="AP5" s="114"/>
+      <c r="AQ5" s="114"/>
+      <c r="AR5" s="114"/>
+      <c r="AS5" s="115"/>
+      <c r="AT5" s="113">
         <f>AT6</f>
         <v>46020</v>
       </c>
-      <c r="AU5" s="107"/>
-      <c r="AV5" s="107"/>
-      <c r="AW5" s="107"/>
-      <c r="AX5" s="107"/>
-      <c r="AY5" s="107"/>
-      <c r="AZ5" s="108"/>
-      <c r="BA5" s="106">
+      <c r="AU5" s="114"/>
+      <c r="AV5" s="114"/>
+      <c r="AW5" s="114"/>
+      <c r="AX5" s="114"/>
+      <c r="AY5" s="114"/>
+      <c r="AZ5" s="115"/>
+      <c r="BA5" s="113">
         <f>BA6</f>
         <v>46027</v>
       </c>
-      <c r="BB5" s="107"/>
-      <c r="BC5" s="107"/>
-      <c r="BD5" s="107"/>
-      <c r="BE5" s="107"/>
-      <c r="BF5" s="107"/>
-      <c r="BG5" s="108"/>
-      <c r="BH5" s="106">
+      <c r="BB5" s="114"/>
+      <c r="BC5" s="114"/>
+      <c r="BD5" s="114"/>
+      <c r="BE5" s="114"/>
+      <c r="BF5" s="114"/>
+      <c r="BG5" s="115"/>
+      <c r="BH5" s="113">
         <f>BH6</f>
         <v>46034</v>
       </c>
-      <c r="BI5" s="107"/>
-      <c r="BJ5" s="107"/>
-      <c r="BK5" s="107"/>
-      <c r="BL5" s="107"/>
-      <c r="BM5" s="107"/>
-      <c r="BN5" s="108"/>
+      <c r="BI5" s="114"/>
+      <c r="BJ5" s="114"/>
+      <c r="BK5" s="114"/>
+      <c r="BL5" s="114"/>
+      <c r="BM5" s="114"/>
+      <c r="BN5" s="115"/>
     </row>
     <row r="6" spans="1:66">
       <c r="A6" s="65"/>
@@ -5957,7 +5997,7 @@
     </row>
     <row r="20" spans="1:66" s="1" customFormat="1" ht="21" customHeight="1">
       <c r="A20" s="4" t="str">
-        <f t="shared" ref="A20:A59" si="14">IF(ISERROR(VALUE(SUBSTITUTE(prevWBS,".",""))),"0.1",IF(ISERROR(FIND("`",SUBSTITUTE(prevWBS,".","`",1))),prevWBS&amp;".1",LEFT(prevWBS,FIND("`",SUBSTITUTE(prevWBS,".","`",1)))&amp;IF(ISERROR(FIND("`",SUBSTITUTE(prevWBS,".","`",2))),VALUE(RIGHT(prevWBS,LEN(prevWBS)-FIND("`",SUBSTITUTE(prevWBS,".","`",1))))+1,VALUE(MID(prevWBS,FIND("`",SUBSTITUTE(prevWBS,".","`",1))+1,(FIND("`",SUBSTITUTE(prevWBS,".","`",2))-FIND("`",SUBSTITUTE(prevWBS,".","`",1))-1)))+1)))</f>
+        <f t="shared" ref="A20:A60" si="14">IF(ISERROR(VALUE(SUBSTITUTE(prevWBS,".",""))),"0.1",IF(ISERROR(FIND("`",SUBSTITUTE(prevWBS,".","`",1))),prevWBS&amp;".1",LEFT(prevWBS,FIND("`",SUBSTITUTE(prevWBS,".","`",1)))&amp;IF(ISERROR(FIND("`",SUBSTITUTE(prevWBS,".","`",2))),VALUE(RIGHT(prevWBS,LEN(prevWBS)-FIND("`",SUBSTITUTE(prevWBS,".","`",1))))+1,VALUE(MID(prevWBS,FIND("`",SUBSTITUTE(prevWBS,".","`",1))+1,(FIND("`",SUBSTITUTE(prevWBS,".","`",2))-FIND("`",SUBSTITUTE(prevWBS,".","`",1))-1)))+1)))</f>
         <v>1.12</v>
       </c>
       <c r="B20" s="89" t="s">
@@ -7284,7 +7324,7 @@
       </c>
       <c r="D35" s="5"/>
       <c r="E35" s="6">
-        <f t="shared" ref="E35:E46" si="27">F33+1</f>
+        <f t="shared" ref="E35:E36" si="27">F33+1</f>
         <v>46073</v>
       </c>
       <c r="F35" s="7">
@@ -7455,12 +7495,12 @@
       <c r="B37" s="105" t="s">
         <v>50</v>
       </c>
-      <c r="C37" s="117" t="s">
+      <c r="C37" s="106" t="s">
         <v>27</v>
       </c>
       <c r="D37" s="5"/>
       <c r="E37" s="6">
-        <f>F35+1</f>
+        <f t="shared" ref="E37:E42" si="28">F35+1</f>
         <v>46077</v>
       </c>
       <c r="F37" s="7">
@@ -7548,11 +7588,11 @@
       </c>
       <c r="D38" s="5"/>
       <c r="E38" s="6">
-        <f>F36+1</f>
+        <f t="shared" si="28"/>
         <v>46077</v>
       </c>
       <c r="F38" s="7">
-        <f t="shared" ref="F38" si="28">IF(ISBLANK(E38)," - ",IF(G38=0,E38,E38+G38-1))</f>
+        <f t="shared" ref="F38" si="29">IF(ISBLANK(E38)," - ",IF(G38=0,E38,E38+G38-1))</f>
         <v>46078</v>
       </c>
       <c r="G38" s="8">
@@ -7562,7 +7602,7 @@
         <v>0</v>
       </c>
       <c r="I38" s="10">
-        <f t="shared" ref="I38" si="29">IF(OR(F38=0,E38=0)," - ",NETWORKDAYS(E38,F38))</f>
+        <f t="shared" ref="I38" si="30">IF(OR(F38=0,E38=0)," - ",NETWORKDAYS(E38,F38))</f>
         <v>2</v>
       </c>
       <c r="J38" s="11"/>
@@ -7636,11 +7676,11 @@
       </c>
       <c r="D39" s="5"/>
       <c r="E39" s="6">
-        <f>F37+1</f>
+        <f t="shared" si="28"/>
         <v>46079</v>
       </c>
       <c r="F39" s="7">
-        <f t="shared" ref="F39" si="30">IF(ISBLANK(E39)," - ",IF(G39=0,E39,E39+G39-1))</f>
+        <f t="shared" ref="F39" si="31">IF(ISBLANK(E39)," - ",IF(G39=0,E39,E39+G39-1))</f>
         <v>46080</v>
       </c>
       <c r="G39" s="8">
@@ -7650,7 +7690,7 @@
         <v>0</v>
       </c>
       <c r="I39" s="10">
-        <f t="shared" ref="I39" si="31">IF(OR(F39=0,E39=0)," - ",NETWORKDAYS(E39,F39))</f>
+        <f t="shared" ref="I39" si="32">IF(OR(F39=0,E39=0)," - ",NETWORKDAYS(E39,F39))</f>
         <v>2</v>
       </c>
       <c r="J39" s="11"/>
@@ -7724,11 +7764,11 @@
       </c>
       <c r="D40" s="5"/>
       <c r="E40" s="6">
-        <f>F38+1</f>
+        <f t="shared" si="28"/>
         <v>46079</v>
       </c>
       <c r="F40" s="7">
-        <f t="shared" ref="F40:F59" si="32">IF(ISBLANK(E40)," - ",IF(G40=0,E40,E40+G40-1))</f>
+        <f t="shared" ref="F40:F60" si="33">IF(ISBLANK(E40)," - ",IF(G40=0,E40,E40+G40-1))</f>
         <v>46080</v>
       </c>
       <c r="G40" s="8">
@@ -7738,7 +7778,7 @@
         <v>0.5</v>
       </c>
       <c r="I40" s="10">
-        <f t="shared" ref="I40:I59" si="33">IF(OR(F40=0,E40=0)," - ",NETWORKDAYS(E40,F40))</f>
+        <f t="shared" ref="I40:I60" si="34">IF(OR(F40=0,E40=0)," - ",NETWORKDAYS(E40,F40))</f>
         <v>2</v>
       </c>
       <c r="J40" s="11"/>
@@ -7812,11 +7852,11 @@
       </c>
       <c r="D41" s="5"/>
       <c r="E41" s="6">
-        <f>F39+1</f>
+        <f t="shared" si="28"/>
         <v>46081</v>
       </c>
       <c r="F41" s="7">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>46084</v>
       </c>
       <c r="G41" s="8">
@@ -7826,7 +7866,7 @@
         <v>0</v>
       </c>
       <c r="I41" s="10">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>2</v>
       </c>
       <c r="J41" s="11"/>
@@ -7900,11 +7940,11 @@
       </c>
       <c r="D42" s="5"/>
       <c r="E42" s="6">
-        <f>F40+1</f>
+        <f t="shared" si="28"/>
         <v>46081</v>
       </c>
       <c r="F42" s="7">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>46084</v>
       </c>
       <c r="G42" s="8">
@@ -7914,7 +7954,7 @@
         <v>0</v>
       </c>
       <c r="I42" s="10">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>2</v>
       </c>
       <c r="J42" s="11"/>
@@ -7983,7 +8023,7 @@
       <c r="B43" s="105" t="s">
         <v>44</v>
       </c>
-      <c r="C43" s="118" t="s">
+      <c r="C43" s="107" t="s">
         <v>239</v>
       </c>
       <c r="D43" s="5"/>
@@ -7992,7 +8032,7 @@
         <v>46084</v>
       </c>
       <c r="F43" s="7">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>46086</v>
       </c>
       <c r="G43" s="8">
@@ -8002,7 +8042,7 @@
         <v>0</v>
       </c>
       <c r="I43" s="10">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>3</v>
       </c>
       <c r="J43" s="11"/>
@@ -8071,7 +8111,7 @@
       <c r="B44" s="105" t="s">
         <v>65</v>
       </c>
-      <c r="C44" s="118" t="s">
+      <c r="C44" s="107" t="s">
         <v>236</v>
       </c>
       <c r="D44" s="5"/>
@@ -8080,7 +8120,7 @@
         <v>46084</v>
       </c>
       <c r="F44" s="7">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>46086</v>
       </c>
       <c r="G44" s="8">
@@ -8090,7 +8130,7 @@
         <v>0</v>
       </c>
       <c r="I44" s="10">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>3</v>
       </c>
       <c r="J44" s="11"/>
@@ -8156,29 +8196,29 @@
         <f t="shared" si="14"/>
         <v>1.37</v>
       </c>
-      <c r="B45" s="93" t="s">
-        <v>52</v>
+      <c r="B45" s="89" t="s">
+        <v>240</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="D45" s="5"/>
       <c r="E45" s="6">
-        <f t="shared" si="27"/>
-        <v>46087</v>
+        <f>F41 + 1</f>
+        <v>46085</v>
       </c>
       <c r="F45" s="7">
-        <f t="shared" si="32"/>
-        <v>46090</v>
+        <f t="shared" ref="F45" si="35">IF(ISBLANK(E45)," - ",IF(G45=0,E45,E45+G45-1))</f>
+        <v>46086</v>
       </c>
       <c r="G45" s="8">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H45" s="9">
         <v>0</v>
       </c>
       <c r="I45" s="10">
-        <f t="shared" si="33"/>
+        <f t="shared" ref="I45" si="36">IF(OR(F45=0,E45=0)," - ",NETWORKDAYS(E45,F45))</f>
         <v>2</v>
       </c>
       <c r="J45" s="11"/>
@@ -8245,18 +8285,18 @@
         <v>1.38</v>
       </c>
       <c r="B46" s="93" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="D46" s="5"/>
       <c r="E46" s="6">
-        <f t="shared" si="27"/>
+        <f>F43+1</f>
         <v>46087</v>
       </c>
       <c r="F46" s="7">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>46090</v>
       </c>
       <c r="G46" s="8">
@@ -8266,7 +8306,7 @@
         <v>0</v>
       </c>
       <c r="I46" s="10">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>2</v>
       </c>
       <c r="J46" s="11"/>
@@ -8333,28 +8373,28 @@
         <v>1.39</v>
       </c>
       <c r="B47" s="93" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="D47" s="5"/>
       <c r="E47" s="6">
-        <f>F45+1</f>
-        <v>46091</v>
+        <f>F44+1</f>
+        <v>46087</v>
       </c>
       <c r="F47" s="7">
-        <f t="shared" si="32"/>
-        <v>46092</v>
+        <f t="shared" si="33"/>
+        <v>46090</v>
       </c>
       <c r="G47" s="8">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H47" s="9">
         <v>0</v>
       </c>
       <c r="I47" s="10">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>2</v>
       </c>
       <c r="J47" s="11"/>
@@ -8421,18 +8461,18 @@
         <v>1.40</v>
       </c>
       <c r="B48" s="93" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="D48" s="5"/>
       <c r="E48" s="6">
-        <f>F46+1</f>
+        <f t="shared" ref="E48:E55" si="37">F46+1</f>
         <v>46091</v>
       </c>
       <c r="F48" s="7">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>46092</v>
       </c>
       <c r="G48" s="8">
@@ -8442,7 +8482,7 @@
         <v>0</v>
       </c>
       <c r="I48" s="10">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>2</v>
       </c>
       <c r="J48" s="11"/>
@@ -8509,19 +8549,19 @@
         <v>1.41</v>
       </c>
       <c r="B49" s="93" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="D49" s="5"/>
       <c r="E49" s="6">
-        <f>F47+1</f>
-        <v>46093</v>
+        <f t="shared" si="37"/>
+        <v>46091</v>
       </c>
       <c r="F49" s="7">
-        <f t="shared" si="32"/>
-        <v>46094</v>
+        <f t="shared" si="33"/>
+        <v>46092</v>
       </c>
       <c r="G49" s="8">
         <v>2</v>
@@ -8530,7 +8570,7 @@
         <v>0</v>
       </c>
       <c r="I49" s="10">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>2</v>
       </c>
       <c r="J49" s="11"/>
@@ -8597,18 +8637,18 @@
         <v>1.42</v>
       </c>
       <c r="B50" s="93" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="D50" s="5"/>
       <c r="E50" s="6">
-        <f>F48+1</f>
+        <f t="shared" si="37"/>
         <v>46093</v>
       </c>
       <c r="F50" s="7">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>46094</v>
       </c>
       <c r="G50" s="8">
@@ -8618,7 +8658,7 @@
         <v>0</v>
       </c>
       <c r="I50" s="10">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>2</v>
       </c>
       <c r="J50" s="11"/>
@@ -8685,28 +8725,28 @@
         <v>1.43</v>
       </c>
       <c r="B51" s="93" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="D51" s="5"/>
       <c r="E51" s="6">
-        <f>F49+1</f>
-        <v>46095</v>
+        <f t="shared" si="37"/>
+        <v>46093</v>
       </c>
       <c r="F51" s="7">
-        <f t="shared" si="32"/>
-        <v>46098</v>
+        <f t="shared" si="33"/>
+        <v>46094</v>
       </c>
       <c r="G51" s="8">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H51" s="9">
         <v>0</v>
       </c>
       <c r="I51" s="10">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>2</v>
       </c>
       <c r="J51" s="11"/>
@@ -8772,19 +8812,19 @@
         <f t="shared" si="14"/>
         <v>1.44</v>
       </c>
-      <c r="B52" s="93" t="s">
-        <v>59</v>
+      <c r="B52" s="105" t="s">
+        <v>58</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="D52" s="5"/>
       <c r="E52" s="6">
-        <f>F50+1</f>
+        <f t="shared" si="37"/>
         <v>46095</v>
       </c>
       <c r="F52" s="7">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>46098</v>
       </c>
       <c r="G52" s="8">
@@ -8794,7 +8834,7 @@
         <v>0</v>
       </c>
       <c r="I52" s="10">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>2</v>
       </c>
       <c r="J52" s="11"/>
@@ -8860,29 +8900,29 @@
         <f t="shared" si="14"/>
         <v>1.45</v>
       </c>
-      <c r="B53" s="93" t="s">
-        <v>60</v>
+      <c r="B53" s="105" t="s">
+        <v>59</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="D53" s="5"/>
       <c r="E53" s="6">
-        <f>F51+1</f>
-        <v>46099</v>
+        <f t="shared" si="37"/>
+        <v>46095</v>
       </c>
       <c r="F53" s="7">
-        <f t="shared" si="32"/>
-        <v>46100</v>
+        <f t="shared" si="33"/>
+        <v>46098</v>
       </c>
       <c r="G53" s="8">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H53" s="9">
         <v>0</v>
       </c>
       <c r="I53" s="10">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>2</v>
       </c>
       <c r="J53" s="11"/>
@@ -8948,19 +8988,19 @@
         <f t="shared" si="14"/>
         <v>1.46</v>
       </c>
-      <c r="B54" s="93" t="s">
-        <v>61</v>
+      <c r="B54" s="105" t="s">
+        <v>60</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="D54" s="5"/>
       <c r="E54" s="6">
-        <f>F52+1</f>
+        <f t="shared" si="37"/>
         <v>46099</v>
       </c>
       <c r="F54" s="7">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>46100</v>
       </c>
       <c r="G54" s="8">
@@ -8970,7 +9010,7 @@
         <v>0</v>
       </c>
       <c r="I54" s="10">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>2</v>
       </c>
       <c r="J54" s="11"/>
@@ -9036,29 +9076,29 @@
         <f t="shared" si="14"/>
         <v>1.47</v>
       </c>
-      <c r="B55" s="93" t="s">
-        <v>62</v>
+      <c r="B55" s="105" t="s">
+        <v>61</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="D55" s="5"/>
       <c r="E55" s="6">
-        <f>F53+9</f>
-        <v>46109</v>
+        <f t="shared" si="37"/>
+        <v>46099</v>
       </c>
       <c r="F55" s="7">
-        <f t="shared" si="32"/>
-        <v>46112</v>
+        <f t="shared" si="33"/>
+        <v>46100</v>
       </c>
       <c r="G55" s="8">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H55" s="9">
         <v>0</v>
       </c>
       <c r="I55" s="10">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>2</v>
       </c>
       <c r="J55" s="11"/>
@@ -9124,11 +9164,11 @@
         <f t="shared" si="14"/>
         <v>1.48</v>
       </c>
-      <c r="B56" s="93" t="s">
-        <v>63</v>
+      <c r="B56" s="105" t="s">
+        <v>62</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="D56" s="5"/>
       <c r="E56" s="6">
@@ -9136,7 +9176,7 @@
         <v>46109</v>
       </c>
       <c r="F56" s="7">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>46112</v>
       </c>
       <c r="G56" s="8">
@@ -9146,7 +9186,7 @@
         <v>0</v>
       </c>
       <c r="I56" s="10">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>2</v>
       </c>
       <c r="J56" s="11"/>
@@ -9213,28 +9253,28 @@
         <v>1.49</v>
       </c>
       <c r="B57" s="93" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="D57" s="5"/>
       <c r="E57" s="6">
-        <f>F55+1</f>
-        <v>46113</v>
+        <f>F55+9</f>
+        <v>46109</v>
       </c>
       <c r="F57" s="7">
-        <f t="shared" si="32"/>
-        <v>46114</v>
+        <f t="shared" si="33"/>
+        <v>46112</v>
       </c>
       <c r="G57" s="8">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H57" s="9">
         <v>0</v>
       </c>
       <c r="I57" s="10">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>2</v>
       </c>
       <c r="J57" s="11"/>
@@ -9300,11 +9340,11 @@
         <f t="shared" si="14"/>
         <v>1.50</v>
       </c>
-      <c r="B58" s="119" t="s">
-        <v>51</v>
-      </c>
-      <c r="C58" s="117" t="s">
-        <v>19</v>
+      <c r="B58" s="105" t="s">
+        <v>64</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>27</v>
       </c>
       <c r="D58" s="5"/>
       <c r="E58" s="6">
@@ -9312,7 +9352,7 @@
         <v>46113</v>
       </c>
       <c r="F58" s="7">
-        <f>IF(ISBLANK(E58)," - ",IF(G58=0,E58,E58+G58-1))</f>
+        <f t="shared" si="33"/>
         <v>46114</v>
       </c>
       <c r="G58" s="8">
@@ -9322,7 +9362,7 @@
         <v>0</v>
       </c>
       <c r="I58" s="10">
-        <f>IF(OR(F58=0,E58=0)," - ",NETWORKDAYS(E58,F58))</f>
+        <f t="shared" si="34"/>
         <v>2</v>
       </c>
       <c r="J58" s="11"/>
@@ -9388,29 +9428,29 @@
         <f t="shared" si="14"/>
         <v>1.51</v>
       </c>
-      <c r="B59" s="93" t="s">
-        <v>66</v>
-      </c>
-      <c r="C59" s="1" t="s">
-        <v>27</v>
+      <c r="B59" s="105" t="s">
+        <v>51</v>
+      </c>
+      <c r="C59" s="106" t="s">
+        <v>19</v>
       </c>
       <c r="D59" s="5"/>
       <c r="E59" s="6">
         <f>F57+1</f>
-        <v>46115</v>
+        <v>46113</v>
       </c>
       <c r="F59" s="7">
-        <f t="shared" si="32"/>
-        <v>46118</v>
+        <f>IF(ISBLANK(E59)," - ",IF(G59=0,E59,E59+G59-1))</f>
+        <v>46114</v>
       </c>
       <c r="G59" s="8">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H59" s="9">
         <v>0</v>
       </c>
       <c r="I59" s="10">
-        <f t="shared" si="33"/>
+        <f>IF(OR(F59=0,E59=0)," - ",NETWORKDAYS(E59,F59))</f>
         <v>2</v>
       </c>
       <c r="J59" s="11"/>
@@ -9471,72 +9511,93 @@
       <c r="BM59" s="4"/>
       <c r="BN59" s="4"/>
     </row>
-    <row r="61" spans="1:66" s="1" customFormat="1" ht="18">
-      <c r="A61" s="4"/>
-      <c r="B61" s="93"/>
-      <c r="D61" s="5"/>
-      <c r="E61" s="6"/>
-      <c r="F61" s="7"/>
-      <c r="G61" s="8"/>
-      <c r="H61" s="9"/>
-      <c r="I61" s="10"/>
-      <c r="J61" s="11"/>
-      <c r="K61" s="4"/>
-      <c r="L61" s="4"/>
-      <c r="M61" s="4"/>
-      <c r="N61" s="4"/>
-      <c r="O61" s="4"/>
-      <c r="P61" s="4"/>
-      <c r="Q61" s="4"/>
-      <c r="R61" s="4"/>
-      <c r="S61" s="4"/>
-      <c r="T61" s="4"/>
-      <c r="U61" s="4"/>
-      <c r="V61" s="4"/>
-      <c r="W61" s="4"/>
-      <c r="X61" s="4"/>
-      <c r="Y61" s="4"/>
-      <c r="Z61" s="4"/>
-      <c r="AA61" s="4"/>
-      <c r="AB61" s="4"/>
-      <c r="AC61" s="4"/>
-      <c r="AD61" s="4"/>
-      <c r="AE61" s="4"/>
-      <c r="AF61" s="4"/>
-      <c r="AG61" s="4"/>
-      <c r="AH61" s="4"/>
-      <c r="AI61" s="4"/>
-      <c r="AJ61" s="4"/>
-      <c r="AK61" s="4"/>
-      <c r="AL61" s="4"/>
-      <c r="AM61" s="4"/>
-      <c r="AN61" s="4"/>
-      <c r="AO61" s="4"/>
-      <c r="AP61" s="4"/>
-      <c r="AQ61" s="4"/>
-      <c r="AR61" s="4"/>
-      <c r="AS61" s="4"/>
-      <c r="AT61" s="4"/>
-      <c r="AU61" s="4"/>
-      <c r="AV61" s="4"/>
-      <c r="AW61" s="4"/>
-      <c r="AX61" s="4"/>
-      <c r="AY61" s="4"/>
-      <c r="AZ61" s="4"/>
-      <c r="BA61" s="4"/>
-      <c r="BB61" s="4"/>
-      <c r="BC61" s="4"/>
-      <c r="BD61" s="4"/>
-      <c r="BE61" s="4"/>
-      <c r="BF61" s="4"/>
-      <c r="BG61" s="4"/>
-      <c r="BH61" s="4"/>
-      <c r="BI61" s="4"/>
-      <c r="BJ61" s="4"/>
-      <c r="BK61" s="4"/>
-      <c r="BL61" s="4"/>
-      <c r="BM61" s="4"/>
-      <c r="BN61" s="4"/>
+    <row r="60" spans="1:66" s="1" customFormat="1" ht="18">
+      <c r="A60" s="4" t="str">
+        <f t="shared" si="14"/>
+        <v>1.52</v>
+      </c>
+      <c r="B60" s="93" t="s">
+        <v>66</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D60" s="5"/>
+      <c r="E60" s="6">
+        <f>F58+1</f>
+        <v>46115</v>
+      </c>
+      <c r="F60" s="7">
+        <f t="shared" si="33"/>
+        <v>46118</v>
+      </c>
+      <c r="G60" s="8">
+        <v>4</v>
+      </c>
+      <c r="H60" s="9">
+        <v>0</v>
+      </c>
+      <c r="I60" s="10">
+        <f t="shared" si="34"/>
+        <v>2</v>
+      </c>
+      <c r="J60" s="11"/>
+      <c r="K60" s="4"/>
+      <c r="L60" s="4"/>
+      <c r="M60" s="4"/>
+      <c r="N60" s="4"/>
+      <c r="O60" s="4"/>
+      <c r="P60" s="4"/>
+      <c r="Q60" s="4"/>
+      <c r="R60" s="4"/>
+      <c r="S60" s="4"/>
+      <c r="T60" s="4"/>
+      <c r="U60" s="4"/>
+      <c r="V60" s="4"/>
+      <c r="W60" s="4"/>
+      <c r="X60" s="4"/>
+      <c r="Y60" s="4"/>
+      <c r="Z60" s="4"/>
+      <c r="AA60" s="4"/>
+      <c r="AB60" s="4"/>
+      <c r="AC60" s="4"/>
+      <c r="AD60" s="4"/>
+      <c r="AE60" s="4"/>
+      <c r="AF60" s="4"/>
+      <c r="AG60" s="4"/>
+      <c r="AH60" s="4"/>
+      <c r="AI60" s="4"/>
+      <c r="AJ60" s="4"/>
+      <c r="AK60" s="4"/>
+      <c r="AL60" s="4"/>
+      <c r="AM60" s="4"/>
+      <c r="AN60" s="4"/>
+      <c r="AO60" s="4"/>
+      <c r="AP60" s="4"/>
+      <c r="AQ60" s="4"/>
+      <c r="AR60" s="4"/>
+      <c r="AS60" s="4"/>
+      <c r="AT60" s="4"/>
+      <c r="AU60" s="4"/>
+      <c r="AV60" s="4"/>
+      <c r="AW60" s="4"/>
+      <c r="AX60" s="4"/>
+      <c r="AY60" s="4"/>
+      <c r="AZ60" s="4"/>
+      <c r="BA60" s="4"/>
+      <c r="BB60" s="4"/>
+      <c r="BC60" s="4"/>
+      <c r="BD60" s="4"/>
+      <c r="BE60" s="4"/>
+      <c r="BF60" s="4"/>
+      <c r="BG60" s="4"/>
+      <c r="BH60" s="4"/>
+      <c r="BI60" s="4"/>
+      <c r="BJ60" s="4"/>
+      <c r="BK60" s="4"/>
+      <c r="BL60" s="4"/>
+      <c r="BM60" s="4"/>
+      <c r="BN60" s="4"/>
     </row>
     <row r="62" spans="1:66" s="1" customFormat="1" ht="18">
       <c r="A62" s="4"/>
@@ -10409,189 +10470,169 @@
       <c r="BM74" s="4"/>
       <c r="BN74" s="4"/>
     </row>
-    <row r="75" spans="1:66" s="55" customFormat="1" ht="18" hidden="1">
-      <c r="A75" s="94" t="str">
+    <row r="75" spans="1:66" s="1" customFormat="1" ht="18">
+      <c r="A75" s="4"/>
+      <c r="B75" s="93"/>
+      <c r="D75" s="5"/>
+      <c r="E75" s="6"/>
+      <c r="F75" s="7"/>
+      <c r="G75" s="8"/>
+      <c r="H75" s="9"/>
+      <c r="I75" s="10"/>
+      <c r="J75" s="11"/>
+      <c r="K75" s="4"/>
+      <c r="L75" s="4"/>
+      <c r="M75" s="4"/>
+      <c r="N75" s="4"/>
+      <c r="O75" s="4"/>
+      <c r="P75" s="4"/>
+      <c r="Q75" s="4"/>
+      <c r="R75" s="4"/>
+      <c r="S75" s="4"/>
+      <c r="T75" s="4"/>
+      <c r="U75" s="4"/>
+      <c r="V75" s="4"/>
+      <c r="W75" s="4"/>
+      <c r="X75" s="4"/>
+      <c r="Y75" s="4"/>
+      <c r="Z75" s="4"/>
+      <c r="AA75" s="4"/>
+      <c r="AB75" s="4"/>
+      <c r="AC75" s="4"/>
+      <c r="AD75" s="4"/>
+      <c r="AE75" s="4"/>
+      <c r="AF75" s="4"/>
+      <c r="AG75" s="4"/>
+      <c r="AH75" s="4"/>
+      <c r="AI75" s="4"/>
+      <c r="AJ75" s="4"/>
+      <c r="AK75" s="4"/>
+      <c r="AL75" s="4"/>
+      <c r="AM75" s="4"/>
+      <c r="AN75" s="4"/>
+      <c r="AO75" s="4"/>
+      <c r="AP75" s="4"/>
+      <c r="AQ75" s="4"/>
+      <c r="AR75" s="4"/>
+      <c r="AS75" s="4"/>
+      <c r="AT75" s="4"/>
+      <c r="AU75" s="4"/>
+      <c r="AV75" s="4"/>
+      <c r="AW75" s="4"/>
+      <c r="AX75" s="4"/>
+      <c r="AY75" s="4"/>
+      <c r="AZ75" s="4"/>
+      <c r="BA75" s="4"/>
+      <c r="BB75" s="4"/>
+      <c r="BC75" s="4"/>
+      <c r="BD75" s="4"/>
+      <c r="BE75" s="4"/>
+      <c r="BF75" s="4"/>
+      <c r="BG75" s="4"/>
+      <c r="BH75" s="4"/>
+      <c r="BI75" s="4"/>
+      <c r="BJ75" s="4"/>
+      <c r="BK75" s="4"/>
+      <c r="BL75" s="4"/>
+      <c r="BM75" s="4"/>
+      <c r="BN75" s="4"/>
+    </row>
+    <row r="76" spans="1:66" s="55" customFormat="1" ht="18" hidden="1">
+      <c r="A76" s="94" t="str">
         <f>IF(ISERROR(VALUE(SUBSTITUTE(prevWBS,".",""))),"1",IF(ISERROR(FIND("`",SUBSTITUTE(prevWBS,".","`",1))),TEXT(VALUE(prevWBS)+1,"#"),TEXT(VALUE(LEFT(prevWBS,FIND("`",SUBSTITUTE(prevWBS,".","`",1))-1))+1,"#")))</f>
         <v>1</v>
       </c>
-      <c r="B75" s="95" t="s">
+      <c r="B76" s="95" t="s">
         <v>67</v>
       </c>
-      <c r="D75" s="96"/>
-      <c r="E75" s="97"/>
-      <c r="F75" s="97" t="str">
-        <f t="shared" ref="F75:F80" si="34">IF(ISBLANK(E75)," - ",IF(G75=0,E75,E75+G75-1))</f>
+      <c r="D76" s="96"/>
+      <c r="E76" s="97"/>
+      <c r="F76" s="97" t="str">
+        <f t="shared" ref="F76:F81" si="38">IF(ISBLANK(E76)," - ",IF(G76=0,E76,E76+G76-1))</f>
         <v xml:space="preserve"> - </v>
       </c>
-      <c r="G75" s="98"/>
-      <c r="H75" s="99"/>
-      <c r="I75" s="100" t="str">
-        <f t="shared" ref="I75:I80" si="35">IF(OR(F75=0,E75=0)," - ",NETWORKDAYS(E75,F75))</f>
+      <c r="G76" s="98"/>
+      <c r="H76" s="99"/>
+      <c r="I76" s="100" t="str">
+        <f t="shared" ref="I76:I81" si="39">IF(OR(F76=0,E76=0)," - ",NETWORKDAYS(E76,F76))</f>
         <v xml:space="preserve"> - </v>
       </c>
-      <c r="J75" s="101"/>
-      <c r="K75" s="102"/>
-      <c r="L75" s="102"/>
-      <c r="M75" s="102"/>
-      <c r="N75" s="102"/>
-      <c r="O75" s="102"/>
-      <c r="P75" s="102"/>
-      <c r="Q75" s="102"/>
-      <c r="R75" s="102"/>
-      <c r="S75" s="102"/>
-      <c r="T75" s="102"/>
-      <c r="U75" s="102"/>
-      <c r="V75" s="102"/>
-      <c r="W75" s="102"/>
-      <c r="X75" s="102"/>
-      <c r="Y75" s="102"/>
-      <c r="Z75" s="102"/>
-      <c r="AA75" s="102"/>
-      <c r="AB75" s="102"/>
-      <c r="AC75" s="102"/>
-      <c r="AD75" s="102"/>
-      <c r="AE75" s="102"/>
-      <c r="AF75" s="102"/>
-      <c r="AG75" s="102"/>
-      <c r="AH75" s="102"/>
-      <c r="AI75" s="102"/>
-      <c r="AJ75" s="102"/>
-      <c r="AK75" s="102"/>
-      <c r="AL75" s="102"/>
-      <c r="AM75" s="102"/>
-      <c r="AN75" s="102"/>
-      <c r="AO75" s="102"/>
-      <c r="AP75" s="102"/>
-      <c r="AQ75" s="102"/>
-      <c r="AR75" s="102"/>
-      <c r="AS75" s="102"/>
-      <c r="AT75" s="102"/>
-      <c r="AU75" s="102"/>
-      <c r="AV75" s="102"/>
-      <c r="AW75" s="102"/>
-      <c r="AX75" s="102"/>
-      <c r="AY75" s="102"/>
-      <c r="AZ75" s="102"/>
-      <c r="BA75" s="102"/>
-      <c r="BB75" s="102"/>
-      <c r="BC75" s="102"/>
-      <c r="BD75" s="102"/>
-      <c r="BE75" s="102"/>
-      <c r="BF75" s="102"/>
-      <c r="BG75" s="102"/>
-      <c r="BH75" s="102"/>
-      <c r="BI75" s="102"/>
-      <c r="BJ75" s="102"/>
-      <c r="BK75" s="102"/>
-      <c r="BL75" s="102"/>
-      <c r="BM75" s="102"/>
-      <c r="BN75" s="102"/>
-    </row>
-    <row r="76" spans="1:66" s="1" customFormat="1" ht="18" hidden="1">
-      <c r="A76" s="4" t="str">
-        <f t="shared" ref="A76:A114" si="36">IF(ISERROR(VALUE(SUBSTITUTE(prevWBS,".",""))),"0.1",IF(ISERROR(FIND("`",SUBSTITUTE(prevWBS,".","`",1))),prevWBS&amp;".1",LEFT(prevWBS,FIND("`",SUBSTITUTE(prevWBS,".","`",1)))&amp;IF(ISERROR(FIND("`",SUBSTITUTE(prevWBS,".","`",2))),VALUE(RIGHT(prevWBS,LEN(prevWBS)-FIND("`",SUBSTITUTE(prevWBS,".","`",1))))+1,VALUE(MID(prevWBS,FIND("`",SUBSTITUTE(prevWBS,".","`",1))+1,(FIND("`",SUBSTITUTE(prevWBS,".","`",2))-FIND("`",SUBSTITUTE(prevWBS,".","`",1))-1)))+1)))</f>
-        <v>1.1</v>
-      </c>
-      <c r="B76" s="93" t="s">
-        <v>68</v>
-      </c>
-      <c r="C76" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="D76" s="5"/>
-      <c r="E76" s="6">
-        <v>46057</v>
-      </c>
-      <c r="F76" s="7">
-        <f t="shared" si="34"/>
-        <v>46063</v>
-      </c>
-      <c r="G76" s="8">
-        <v>7</v>
-      </c>
-      <c r="H76" s="9">
-        <v>0</v>
-      </c>
-      <c r="I76" s="10">
-        <f t="shared" si="35"/>
-        <v>5</v>
-      </c>
-      <c r="J76" s="11"/>
-      <c r="K76" s="4"/>
-      <c r="L76" s="4"/>
-      <c r="M76" s="4"/>
-      <c r="N76" s="4"/>
-      <c r="O76" s="4"/>
-      <c r="P76" s="4"/>
-      <c r="Q76" s="4"/>
-      <c r="R76" s="4"/>
-      <c r="S76" s="4"/>
-      <c r="T76" s="4"/>
-      <c r="U76" s="4"/>
-      <c r="V76" s="4"/>
-      <c r="W76" s="4"/>
-      <c r="X76" s="4"/>
-      <c r="Y76" s="4"/>
-      <c r="Z76" s="4"/>
-      <c r="AA76" s="4"/>
-      <c r="AB76" s="4"/>
-      <c r="AC76" s="4"/>
-      <c r="AD76" s="4"/>
-      <c r="AE76" s="4"/>
-      <c r="AF76" s="4"/>
-      <c r="AG76" s="4"/>
-      <c r="AH76" s="4"/>
-      <c r="AI76" s="4"/>
-      <c r="AJ76" s="4"/>
-      <c r="AK76" s="4"/>
-      <c r="AL76" s="4"/>
-      <c r="AM76" s="4"/>
-      <c r="AN76" s="4"/>
-      <c r="AO76" s="4"/>
-      <c r="AP76" s="4"/>
-      <c r="AQ76" s="4"/>
-      <c r="AR76" s="4"/>
-      <c r="AS76" s="4"/>
-      <c r="AT76" s="4"/>
-      <c r="AU76" s="4"/>
-      <c r="AV76" s="4"/>
-      <c r="AW76" s="4"/>
-      <c r="AX76" s="4"/>
-      <c r="AY76" s="4"/>
-      <c r="AZ76" s="4"/>
-      <c r="BA76" s="4"/>
-      <c r="BB76" s="4"/>
-      <c r="BC76" s="4"/>
-      <c r="BD76" s="4"/>
-      <c r="BE76" s="4"/>
-      <c r="BF76" s="4"/>
-      <c r="BG76" s="4"/>
-      <c r="BH76" s="4"/>
-      <c r="BI76" s="4"/>
-      <c r="BJ76" s="4"/>
-      <c r="BK76" s="4"/>
-      <c r="BL76" s="4"/>
-      <c r="BM76" s="4"/>
-      <c r="BN76" s="4"/>
+      <c r="J76" s="101"/>
+      <c r="K76" s="102"/>
+      <c r="L76" s="102"/>
+      <c r="M76" s="102"/>
+      <c r="N76" s="102"/>
+      <c r="O76" s="102"/>
+      <c r="P76" s="102"/>
+      <c r="Q76" s="102"/>
+      <c r="R76" s="102"/>
+      <c r="S76" s="102"/>
+      <c r="T76" s="102"/>
+      <c r="U76" s="102"/>
+      <c r="V76" s="102"/>
+      <c r="W76" s="102"/>
+      <c r="X76" s="102"/>
+      <c r="Y76" s="102"/>
+      <c r="Z76" s="102"/>
+      <c r="AA76" s="102"/>
+      <c r="AB76" s="102"/>
+      <c r="AC76" s="102"/>
+      <c r="AD76" s="102"/>
+      <c r="AE76" s="102"/>
+      <c r="AF76" s="102"/>
+      <c r="AG76" s="102"/>
+      <c r="AH76" s="102"/>
+      <c r="AI76" s="102"/>
+      <c r="AJ76" s="102"/>
+      <c r="AK76" s="102"/>
+      <c r="AL76" s="102"/>
+      <c r="AM76" s="102"/>
+      <c r="AN76" s="102"/>
+      <c r="AO76" s="102"/>
+      <c r="AP76" s="102"/>
+      <c r="AQ76" s="102"/>
+      <c r="AR76" s="102"/>
+      <c r="AS76" s="102"/>
+      <c r="AT76" s="102"/>
+      <c r="AU76" s="102"/>
+      <c r="AV76" s="102"/>
+      <c r="AW76" s="102"/>
+      <c r="AX76" s="102"/>
+      <c r="AY76" s="102"/>
+      <c r="AZ76" s="102"/>
+      <c r="BA76" s="102"/>
+      <c r="BB76" s="102"/>
+      <c r="BC76" s="102"/>
+      <c r="BD76" s="102"/>
+      <c r="BE76" s="102"/>
+      <c r="BF76" s="102"/>
+      <c r="BG76" s="102"/>
+      <c r="BH76" s="102"/>
+      <c r="BI76" s="102"/>
+      <c r="BJ76" s="102"/>
+      <c r="BK76" s="102"/>
+      <c r="BL76" s="102"/>
+      <c r="BM76" s="102"/>
+      <c r="BN76" s="102"/>
     </row>
     <row r="77" spans="1:66" s="1" customFormat="1" ht="18" hidden="1">
       <c r="A77" s="4" t="str">
-        <f t="shared" si="36"/>
-        <v>1.2</v>
+        <f t="shared" ref="A77:A115" si="40">IF(ISERROR(VALUE(SUBSTITUTE(prevWBS,".",""))),"0.1",IF(ISERROR(FIND("`",SUBSTITUTE(prevWBS,".","`",1))),prevWBS&amp;".1",LEFT(prevWBS,FIND("`",SUBSTITUTE(prevWBS,".","`",1)))&amp;IF(ISERROR(FIND("`",SUBSTITUTE(prevWBS,".","`",2))),VALUE(RIGHT(prevWBS,LEN(prevWBS)-FIND("`",SUBSTITUTE(prevWBS,".","`",1))))+1,VALUE(MID(prevWBS,FIND("`",SUBSTITUTE(prevWBS,".","`",1))+1,(FIND("`",SUBSTITUTE(prevWBS,".","`",2))-FIND("`",SUBSTITUTE(prevWBS,".","`",1))-1)))+1)))</f>
+        <v>1.1</v>
       </c>
       <c r="B77" s="93" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>19</v>
+        <v>69</v>
       </c>
       <c r="D77" s="5"/>
       <c r="E77" s="6">
-        <v>46064</v>
+        <v>46057</v>
       </c>
       <c r="F77" s="7">
-        <f t="shared" si="34"/>
-        <v>46070</v>
+        <f t="shared" si="38"/>
+        <v>46063</v>
       </c>
       <c r="G77" s="8">
         <v>7</v>
@@ -10600,7 +10641,7 @@
         <v>0</v>
       </c>
       <c r="I77" s="10">
-        <f t="shared" si="35"/>
+        <f t="shared" si="39"/>
         <v>5</v>
       </c>
       <c r="J77" s="11"/>
@@ -10661,23 +10702,23 @@
       <c r="BM77" s="4"/>
       <c r="BN77" s="4"/>
     </row>
-    <row r="78" spans="1:66" s="1" customFormat="1" ht="44.25" hidden="1" customHeight="1">
+    <row r="78" spans="1:66" s="1" customFormat="1" ht="18" hidden="1">
       <c r="A78" s="4" t="str">
-        <f t="shared" si="36"/>
-        <v>1.3</v>
+        <f t="shared" si="40"/>
+        <v>1.2</v>
       </c>
       <c r="B78" s="93" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="D78" s="5"/>
       <c r="E78" s="6">
         <v>46064</v>
       </c>
       <c r="F78" s="7">
-        <f t="shared" si="34"/>
+        <f t="shared" si="38"/>
         <v>46070</v>
       </c>
       <c r="G78" s="8">
@@ -10687,7 +10728,7 @@
         <v>0</v>
       </c>
       <c r="I78" s="10">
-        <f t="shared" si="35"/>
+        <f t="shared" si="39"/>
         <v>5</v>
       </c>
       <c r="J78" s="11"/>
@@ -10748,24 +10789,24 @@
       <c r="BM78" s="4"/>
       <c r="BN78" s="4"/>
     </row>
-    <row r="79" spans="1:66" s="1" customFormat="1" ht="18" hidden="1">
+    <row r="79" spans="1:66" s="1" customFormat="1" ht="44.25" hidden="1" customHeight="1">
       <c r="A79" s="4" t="str">
-        <f t="shared" si="36"/>
-        <v>1.4</v>
+        <f t="shared" si="40"/>
+        <v>1.3</v>
       </c>
       <c r="B79" s="93" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="D79" s="5"/>
       <c r="E79" s="6">
-        <v>46071</v>
+        <v>46064</v>
       </c>
       <c r="F79" s="7">
-        <f t="shared" si="34"/>
-        <v>46077</v>
+        <f t="shared" si="38"/>
+        <v>46070</v>
       </c>
       <c r="G79" s="8">
         <v>7</v>
@@ -10774,7 +10815,7 @@
         <v>0</v>
       </c>
       <c r="I79" s="10">
-        <f t="shared" si="35"/>
+        <f t="shared" si="39"/>
         <v>5</v>
       </c>
       <c r="J79" s="11"/>
@@ -10837,21 +10878,21 @@
     </row>
     <row r="80" spans="1:66" s="1" customFormat="1" ht="18" hidden="1">
       <c r="A80" s="4" t="str">
-        <f t="shared" si="36"/>
-        <v>1.5</v>
+        <f t="shared" si="40"/>
+        <v>1.4</v>
       </c>
       <c r="B80" s="93" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="D80" s="5"/>
       <c r="E80" s="6">
         <v>46071</v>
       </c>
       <c r="F80" s="7">
-        <f t="shared" si="34"/>
+        <f t="shared" si="38"/>
         <v>46077</v>
       </c>
       <c r="G80" s="8">
@@ -10861,7 +10902,7 @@
         <v>0</v>
       </c>
       <c r="I80" s="10">
-        <f t="shared" si="35"/>
+        <f t="shared" si="39"/>
         <v>5</v>
       </c>
       <c r="J80" s="11"/>
@@ -10924,22 +10965,22 @@
     </row>
     <row r="81" spans="1:66" s="1" customFormat="1" ht="18" hidden="1">
       <c r="A81" s="4" t="str">
-        <f t="shared" si="36"/>
-        <v>1.6</v>
+        <f t="shared" si="40"/>
+        <v>1.5</v>
       </c>
       <c r="B81" s="93" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="D81" s="5"/>
       <c r="E81" s="6">
-        <v>46078</v>
+        <v>46071</v>
       </c>
       <c r="F81" s="7">
-        <f t="shared" ref="F81:F95" si="37">IF(ISBLANK(E81)," - ",IF(G81=0,E81,E81+G81-1))</f>
-        <v>46084</v>
+        <f t="shared" si="38"/>
+        <v>46077</v>
       </c>
       <c r="G81" s="8">
         <v>7</v>
@@ -10948,7 +10989,7 @@
         <v>0</v>
       </c>
       <c r="I81" s="10">
-        <f t="shared" ref="I81:I95" si="38">IF(OR(F81=0,E81=0)," - ",NETWORKDAYS(E81,F81))</f>
+        <f t="shared" si="39"/>
         <v>5</v>
       </c>
       <c r="J81" s="11"/>
@@ -11011,21 +11052,21 @@
     </row>
     <row r="82" spans="1:66" s="1" customFormat="1" ht="18" hidden="1">
       <c r="A82" s="4" t="str">
-        <f t="shared" si="36"/>
-        <v>1.7</v>
+        <f t="shared" si="40"/>
+        <v>1.6</v>
       </c>
       <c r="B82" s="93" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="D82" s="5"/>
       <c r="E82" s="6">
         <v>46078</v>
       </c>
       <c r="F82" s="7">
-        <f t="shared" si="37"/>
+        <f t="shared" ref="F82:F96" si="41">IF(ISBLANK(E82)," - ",IF(G82=0,E82,E82+G82-1))</f>
         <v>46084</v>
       </c>
       <c r="G82" s="8">
@@ -11035,7 +11076,7 @@
         <v>0</v>
       </c>
       <c r="I82" s="10">
-        <f t="shared" si="38"/>
+        <f t="shared" ref="I82:I96" si="42">IF(OR(F82=0,E82=0)," - ",NETWORKDAYS(E82,F82))</f>
         <v>5</v>
       </c>
       <c r="J82" s="11"/>
@@ -11098,22 +11139,22 @@
     </row>
     <row r="83" spans="1:66" s="1" customFormat="1" ht="18" hidden="1">
       <c r="A83" s="4" t="str">
-        <f t="shared" si="36"/>
-        <v>1.8</v>
+        <f t="shared" si="40"/>
+        <v>1.7</v>
       </c>
       <c r="B83" s="93" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>77</v>
+        <v>27</v>
       </c>
       <c r="D83" s="5"/>
       <c r="E83" s="6">
-        <v>46057</v>
+        <v>46078</v>
       </c>
       <c r="F83" s="7">
-        <f t="shared" si="37"/>
-        <v>46063</v>
+        <f t="shared" si="41"/>
+        <v>46084</v>
       </c>
       <c r="G83" s="8">
         <v>7</v>
@@ -11122,7 +11163,7 @@
         <v>0</v>
       </c>
       <c r="I83" s="10">
-        <f t="shared" si="38"/>
+        <f t="shared" si="42"/>
         <v>5</v>
       </c>
       <c r="J83" s="11"/>
@@ -11185,22 +11226,22 @@
     </row>
     <row r="84" spans="1:66" s="1" customFormat="1" ht="18" hidden="1">
       <c r="A84" s="4" t="str">
-        <f t="shared" si="36"/>
-        <v>1.9</v>
+        <f t="shared" si="40"/>
+        <v>1.8</v>
       </c>
       <c r="B84" s="93" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>19</v>
+        <v>77</v>
       </c>
       <c r="D84" s="5"/>
       <c r="E84" s="6">
-        <v>46085</v>
+        <v>46057</v>
       </c>
       <c r="F84" s="7">
-        <f t="shared" si="37"/>
-        <v>46091</v>
+        <f t="shared" si="41"/>
+        <v>46063</v>
       </c>
       <c r="G84" s="8">
         <v>7</v>
@@ -11209,7 +11250,7 @@
         <v>0</v>
       </c>
       <c r="I84" s="10">
-        <f t="shared" si="38"/>
+        <f t="shared" si="42"/>
         <v>5</v>
       </c>
       <c r="J84" s="11"/>
@@ -11272,21 +11313,21 @@
     </row>
     <row r="85" spans="1:66" s="1" customFormat="1" ht="18" hidden="1">
       <c r="A85" s="4" t="str">
-        <f t="shared" si="36"/>
-        <v>1.10</v>
+        <f t="shared" si="40"/>
+        <v>1.9</v>
       </c>
       <c r="B85" s="93" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="D85" s="5"/>
       <c r="E85" s="6">
         <v>46085</v>
       </c>
       <c r="F85" s="7">
-        <f t="shared" si="37"/>
+        <f t="shared" si="41"/>
         <v>46091</v>
       </c>
       <c r="G85" s="8">
@@ -11296,7 +11337,7 @@
         <v>0</v>
       </c>
       <c r="I85" s="10">
-        <f t="shared" si="38"/>
+        <f t="shared" si="42"/>
         <v>5</v>
       </c>
       <c r="J85" s="11"/>
@@ -11359,22 +11400,22 @@
     </row>
     <row r="86" spans="1:66" s="1" customFormat="1" ht="18" hidden="1">
       <c r="A86" s="4" t="str">
-        <f t="shared" si="36"/>
-        <v>1.11</v>
+        <f t="shared" si="40"/>
+        <v>1.10</v>
       </c>
       <c r="B86" s="93" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C86" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D86" s="5"/>
       <c r="E86" s="6">
-        <v>46092</v>
+        <v>46085</v>
       </c>
       <c r="F86" s="7">
-        <f t="shared" si="37"/>
-        <v>46098</v>
+        <f t="shared" si="41"/>
+        <v>46091</v>
       </c>
       <c r="G86" s="8">
         <v>7</v>
@@ -11383,7 +11424,7 @@
         <v>0</v>
       </c>
       <c r="I86" s="10">
-        <f t="shared" si="38"/>
+        <f t="shared" si="42"/>
         <v>5</v>
       </c>
       <c r="J86" s="11"/>
@@ -11446,21 +11487,21 @@
     </row>
     <row r="87" spans="1:66" s="1" customFormat="1" ht="18" hidden="1">
       <c r="A87" s="4" t="str">
-        <f t="shared" si="36"/>
-        <v>1.12</v>
+        <f t="shared" si="40"/>
+        <v>1.11</v>
       </c>
       <c r="B87" s="93" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="D87" s="5"/>
       <c r="E87" s="6">
         <v>46092</v>
       </c>
       <c r="F87" s="7">
-        <f t="shared" si="37"/>
+        <f t="shared" si="41"/>
         <v>46098</v>
       </c>
       <c r="G87" s="8">
@@ -11470,7 +11511,7 @@
         <v>0</v>
       </c>
       <c r="I87" s="10">
-        <f t="shared" si="38"/>
+        <f t="shared" si="42"/>
         <v>5</v>
       </c>
       <c r="J87" s="11"/>
@@ -11533,22 +11574,22 @@
     </row>
     <row r="88" spans="1:66" s="1" customFormat="1" ht="18" hidden="1">
       <c r="A88" s="4" t="str">
-        <f t="shared" si="36"/>
-        <v>1.13</v>
+        <f t="shared" si="40"/>
+        <v>1.12</v>
       </c>
       <c r="B88" s="93" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="D88" s="5"/>
       <c r="E88" s="6">
-        <v>46099</v>
+        <v>46092</v>
       </c>
       <c r="F88" s="7">
-        <f t="shared" si="37"/>
-        <v>46105</v>
+        <f t="shared" si="41"/>
+        <v>46098</v>
       </c>
       <c r="G88" s="8">
         <v>7</v>
@@ -11557,7 +11598,7 @@
         <v>0</v>
       </c>
       <c r="I88" s="10">
-        <f t="shared" si="38"/>
+        <f t="shared" si="42"/>
         <v>5</v>
       </c>
       <c r="J88" s="11"/>
@@ -11620,22 +11661,22 @@
     </row>
     <row r="89" spans="1:66" s="1" customFormat="1" ht="18" hidden="1">
       <c r="A89" s="4" t="str">
-        <f t="shared" si="36"/>
-        <v>1.14</v>
+        <f t="shared" si="40"/>
+        <v>1.13</v>
       </c>
       <c r="B89" s="93" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C89" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D89" s="5"/>
       <c r="E89" s="6">
-        <v>46106</v>
+        <v>46099</v>
       </c>
       <c r="F89" s="7">
-        <f t="shared" ref="F89" si="39">IF(ISBLANK(E89)," - ",IF(G89=0,E89,E89+G89-1))</f>
-        <v>46112</v>
+        <f t="shared" si="41"/>
+        <v>46105</v>
       </c>
       <c r="G89" s="8">
         <v>7</v>
@@ -11644,7 +11685,7 @@
         <v>0</v>
       </c>
       <c r="I89" s="10">
-        <f t="shared" ref="I89" si="40">IF(OR(F89=0,E89=0)," - ",NETWORKDAYS(E89,F89))</f>
+        <f t="shared" si="42"/>
         <v>5</v>
       </c>
       <c r="J89" s="11"/>
@@ -11707,11 +11748,11 @@
     </row>
     <row r="90" spans="1:66" s="1" customFormat="1" ht="18" hidden="1">
       <c r="A90" s="4" t="str">
-        <f t="shared" si="36"/>
-        <v>1.15</v>
+        <f t="shared" si="40"/>
+        <v>1.14</v>
       </c>
       <c r="B90" s="93" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C90" s="1" t="s">
         <v>27</v>
@@ -11721,7 +11762,7 @@
         <v>46106</v>
       </c>
       <c r="F90" s="7">
-        <f t="shared" ref="F90" si="41">IF(ISBLANK(E90)," - ",IF(G90=0,E90,E90+G90-1))</f>
+        <f t="shared" ref="F90" si="43">IF(ISBLANK(E90)," - ",IF(G90=0,E90,E90+G90-1))</f>
         <v>46112</v>
       </c>
       <c r="G90" s="8">
@@ -11731,7 +11772,7 @@
         <v>0</v>
       </c>
       <c r="I90" s="10">
-        <f t="shared" ref="I90" si="42">IF(OR(F90=0,E90=0)," - ",NETWORKDAYS(E90,F90))</f>
+        <f t="shared" ref="I90" si="44">IF(OR(F90=0,E90=0)," - ",NETWORKDAYS(E90,F90))</f>
         <v>5</v>
       </c>
       <c r="J90" s="11"/>
@@ -11794,22 +11835,22 @@
     </row>
     <row r="91" spans="1:66" s="1" customFormat="1" ht="18" hidden="1">
       <c r="A91" s="4" t="str">
-        <f t="shared" si="36"/>
-        <v>1.16</v>
+        <f t="shared" si="40"/>
+        <v>1.15</v>
       </c>
       <c r="B91" s="93" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C91" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D91" s="5"/>
       <c r="E91" s="6">
-        <v>46113</v>
+        <v>46106</v>
       </c>
       <c r="F91" s="7">
-        <f t="shared" si="37"/>
-        <v>46119</v>
+        <f t="shared" ref="F91" si="45">IF(ISBLANK(E91)," - ",IF(G91=0,E91,E91+G91-1))</f>
+        <v>46112</v>
       </c>
       <c r="G91" s="8">
         <v>7</v>
@@ -11818,7 +11859,7 @@
         <v>0</v>
       </c>
       <c r="I91" s="10">
-        <f t="shared" si="38"/>
+        <f t="shared" ref="I91" si="46">IF(OR(F91=0,E91=0)," - ",NETWORKDAYS(E91,F91))</f>
         <v>5</v>
       </c>
       <c r="J91" s="11"/>
@@ -11881,21 +11922,21 @@
     </row>
     <row r="92" spans="1:66" s="1" customFormat="1" ht="18" hidden="1">
       <c r="A92" s="4" t="str">
-        <f t="shared" si="36"/>
-        <v>1.17</v>
+        <f t="shared" si="40"/>
+        <v>1.16</v>
       </c>
       <c r="B92" s="93" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="D92" s="5"/>
       <c r="E92" s="6">
         <v>46113</v>
       </c>
       <c r="F92" s="7">
-        <f t="shared" si="37"/>
+        <f t="shared" si="41"/>
         <v>46119</v>
       </c>
       <c r="G92" s="8">
@@ -11905,7 +11946,7 @@
         <v>0</v>
       </c>
       <c r="I92" s="10">
-        <f t="shared" si="38"/>
+        <f t="shared" si="42"/>
         <v>5</v>
       </c>
       <c r="J92" s="11"/>
@@ -11968,22 +12009,22 @@
     </row>
     <row r="93" spans="1:66" s="1" customFormat="1" ht="18" hidden="1">
       <c r="A93" s="4" t="str">
-        <f t="shared" si="36"/>
-        <v>1.18</v>
+        <f t="shared" si="40"/>
+        <v>1.17</v>
       </c>
       <c r="B93" s="93" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="D93" s="5"/>
       <c r="E93" s="6">
-        <v>46120</v>
+        <v>46113</v>
       </c>
       <c r="F93" s="7">
-        <f t="shared" si="37"/>
-        <v>46126</v>
+        <f t="shared" si="41"/>
+        <v>46119</v>
       </c>
       <c r="G93" s="8">
         <v>7</v>
@@ -11992,7 +12033,7 @@
         <v>0</v>
       </c>
       <c r="I93" s="10">
-        <f t="shared" si="38"/>
+        <f t="shared" si="42"/>
         <v>5</v>
       </c>
       <c r="J93" s="11"/>
@@ -12055,21 +12096,21 @@
     </row>
     <row r="94" spans="1:66" s="1" customFormat="1" ht="18" hidden="1">
       <c r="A94" s="4" t="str">
-        <f t="shared" si="36"/>
-        <v>1.19</v>
+        <f t="shared" si="40"/>
+        <v>1.18</v>
       </c>
       <c r="B94" s="93" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="D94" s="5"/>
       <c r="E94" s="6">
         <v>46120</v>
       </c>
       <c r="F94" s="7">
-        <f t="shared" si="37"/>
+        <f t="shared" si="41"/>
         <v>46126</v>
       </c>
       <c r="G94" s="8">
@@ -12079,7 +12120,7 @@
         <v>0</v>
       </c>
       <c r="I94" s="10">
-        <f t="shared" si="38"/>
+        <f t="shared" si="42"/>
         <v>5</v>
       </c>
       <c r="J94" s="11"/>
@@ -12142,22 +12183,22 @@
     </row>
     <row r="95" spans="1:66" s="1" customFormat="1" ht="18" hidden="1">
       <c r="A95" s="4" t="str">
-        <f t="shared" si="36"/>
-        <v>1.20</v>
+        <f t="shared" si="40"/>
+        <v>1.19</v>
       </c>
       <c r="B95" s="93" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="D95" s="5"/>
       <c r="E95" s="6">
-        <v>46127</v>
+        <v>46120</v>
       </c>
       <c r="F95" s="7">
-        <f t="shared" si="37"/>
-        <v>46133</v>
+        <f t="shared" si="41"/>
+        <v>46126</v>
       </c>
       <c r="G95" s="8">
         <v>7</v>
@@ -12166,7 +12207,7 @@
         <v>0</v>
       </c>
       <c r="I95" s="10">
-        <f t="shared" si="38"/>
+        <f t="shared" si="42"/>
         <v>5</v>
       </c>
       <c r="J95" s="11"/>
@@ -12229,21 +12270,21 @@
     </row>
     <row r="96" spans="1:66" s="1" customFormat="1" ht="18" hidden="1">
       <c r="A96" s="4" t="str">
-        <f t="shared" si="36"/>
-        <v>1.21</v>
+        <f t="shared" si="40"/>
+        <v>1.20</v>
       </c>
       <c r="B96" s="93" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="D96" s="5"/>
       <c r="E96" s="6">
         <v>46127</v>
       </c>
       <c r="F96" s="7">
-        <f t="shared" ref="F96:F106" si="43">IF(ISBLANK(E96)," - ",IF(G96=0,E96,E96+G96-1))</f>
+        <f t="shared" si="41"/>
         <v>46133</v>
       </c>
       <c r="G96" s="8">
@@ -12253,7 +12294,7 @@
         <v>0</v>
       </c>
       <c r="I96" s="10">
-        <f t="shared" ref="I96:I104" si="44">IF(OR(F96=0,E96=0)," - ",NETWORKDAYS(E96,F96))</f>
+        <f t="shared" si="42"/>
         <v>5</v>
       </c>
       <c r="J96" s="11"/>
@@ -12316,22 +12357,22 @@
     </row>
     <row r="97" spans="1:66" s="1" customFormat="1" ht="18" hidden="1">
       <c r="A97" s="4" t="str">
-        <f t="shared" si="36"/>
-        <v>1.22</v>
+        <f t="shared" si="40"/>
+        <v>1.21</v>
       </c>
       <c r="B97" s="93" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="D97" s="5"/>
       <c r="E97" s="6">
-        <v>46134</v>
+        <v>46127</v>
       </c>
       <c r="F97" s="7">
-        <f t="shared" si="43"/>
-        <v>46140</v>
+        <f t="shared" ref="F97:F107" si="47">IF(ISBLANK(E97)," - ",IF(G97=0,E97,E97+G97-1))</f>
+        <v>46133</v>
       </c>
       <c r="G97" s="8">
         <v>7</v>
@@ -12340,7 +12381,7 @@
         <v>0</v>
       </c>
       <c r="I97" s="10">
-        <f t="shared" si="44"/>
+        <f t="shared" ref="I97:I105" si="48">IF(OR(F97=0,E97=0)," - ",NETWORKDAYS(E97,F97))</f>
         <v>5</v>
       </c>
       <c r="J97" s="11"/>
@@ -12403,21 +12444,21 @@
     </row>
     <row r="98" spans="1:66" s="1" customFormat="1" ht="18" hidden="1">
       <c r="A98" s="4" t="str">
-        <f t="shared" si="36"/>
-        <v>1.23</v>
+        <f t="shared" si="40"/>
+        <v>1.22</v>
       </c>
       <c r="B98" s="93" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="D98" s="5"/>
       <c r="E98" s="6">
         <v>46134</v>
       </c>
       <c r="F98" s="7">
-        <f t="shared" ref="F98:F99" si="45">IF(ISBLANK(E98)," - ",IF(G98=0,E98,E98+G98-1))</f>
+        <f t="shared" si="47"/>
         <v>46140</v>
       </c>
       <c r="G98" s="8">
@@ -12427,7 +12468,7 @@
         <v>0</v>
       </c>
       <c r="I98" s="10">
-        <f t="shared" ref="I98:I99" si="46">IF(OR(F98=0,E98=0)," - ",NETWORKDAYS(E98,F98))</f>
+        <f t="shared" si="48"/>
         <v>5</v>
       </c>
       <c r="J98" s="11"/>
@@ -12490,22 +12531,22 @@
     </row>
     <row r="99" spans="1:66" s="1" customFormat="1" ht="18" hidden="1">
       <c r="A99" s="4" t="str">
-        <f t="shared" si="36"/>
-        <v>1.24</v>
+        <f t="shared" si="40"/>
+        <v>1.23</v>
       </c>
       <c r="B99" s="93" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="D99" s="5"/>
       <c r="E99" s="6">
-        <v>46141</v>
+        <v>46134</v>
       </c>
       <c r="F99" s="7">
-        <f t="shared" si="45"/>
-        <v>46147</v>
+        <f t="shared" ref="F99:F100" si="49">IF(ISBLANK(E99)," - ",IF(G99=0,E99,E99+G99-1))</f>
+        <v>46140</v>
       </c>
       <c r="G99" s="8">
         <v>7</v>
@@ -12514,7 +12555,7 @@
         <v>0</v>
       </c>
       <c r="I99" s="10">
-        <f t="shared" si="46"/>
+        <f t="shared" ref="I99:I100" si="50">IF(OR(F99=0,E99=0)," - ",NETWORKDAYS(E99,F99))</f>
         <v>5</v>
       </c>
       <c r="J99" s="11"/>
@@ -12577,11 +12618,11 @@
     </row>
     <row r="100" spans="1:66" s="1" customFormat="1" ht="18" hidden="1">
       <c r="A100" s="4" t="str">
-        <f t="shared" si="36"/>
-        <v>1.25</v>
+        <f t="shared" si="40"/>
+        <v>1.24</v>
       </c>
       <c r="B100" s="93" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C100" s="1" t="s">
         <v>27</v>
@@ -12591,7 +12632,7 @@
         <v>46141</v>
       </c>
       <c r="F100" s="7">
-        <f t="shared" ref="F100:F102" si="47">IF(ISBLANK(E100)," - ",IF(G100=0,E100,E100+G100-1))</f>
+        <f t="shared" si="49"/>
         <v>46147</v>
       </c>
       <c r="G100" s="8">
@@ -12601,7 +12642,7 @@
         <v>0</v>
       </c>
       <c r="I100" s="10">
-        <f t="shared" ref="I100:I102" si="48">IF(OR(F100=0,E100=0)," - ",NETWORKDAYS(E100,F100))</f>
+        <f t="shared" si="50"/>
         <v>5</v>
       </c>
       <c r="J100" s="11"/>
@@ -12664,22 +12705,22 @@
     </row>
     <row r="101" spans="1:66" s="1" customFormat="1" ht="18" hidden="1">
       <c r="A101" s="4" t="str">
-        <f t="shared" si="36"/>
-        <v>1.26</v>
+        <f t="shared" si="40"/>
+        <v>1.25</v>
       </c>
       <c r="B101" s="93" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C101" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D101" s="5"/>
       <c r="E101" s="6">
-        <v>46148</v>
+        <v>46141</v>
       </c>
       <c r="F101" s="7">
-        <f t="shared" si="47"/>
-        <v>46154</v>
+        <f t="shared" ref="F101:F103" si="51">IF(ISBLANK(E101)," - ",IF(G101=0,E101,E101+G101-1))</f>
+        <v>46147</v>
       </c>
       <c r="G101" s="8">
         <v>7</v>
@@ -12688,7 +12729,7 @@
         <v>0</v>
       </c>
       <c r="I101" s="10">
-        <f t="shared" si="48"/>
+        <f t="shared" ref="I101:I103" si="52">IF(OR(F101=0,E101=0)," - ",NETWORKDAYS(E101,F101))</f>
         <v>5</v>
       </c>
       <c r="J101" s="11"/>
@@ -12751,11 +12792,11 @@
     </row>
     <row r="102" spans="1:66" s="1" customFormat="1" ht="18" hidden="1">
       <c r="A102" s="4" t="str">
-        <f t="shared" si="36"/>
-        <v>1.27</v>
+        <f t="shared" si="40"/>
+        <v>1.26</v>
       </c>
       <c r="B102" s="93" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C102" s="1" t="s">
         <v>27</v>
@@ -12765,7 +12806,7 @@
         <v>46148</v>
       </c>
       <c r="F102" s="7">
-        <f t="shared" si="47"/>
+        <f t="shared" si="51"/>
         <v>46154</v>
       </c>
       <c r="G102" s="8">
@@ -12775,7 +12816,7 @@
         <v>0</v>
       </c>
       <c r="I102" s="10">
-        <f t="shared" si="48"/>
+        <f t="shared" si="52"/>
         <v>5</v>
       </c>
       <c r="J102" s="11"/>
@@ -12836,198 +12877,199 @@
       <c r="BM102" s="4"/>
       <c r="BN102" s="4"/>
     </row>
-    <row r="103" spans="1:66" s="55" customFormat="1" ht="18" hidden="1">
-      <c r="A103" s="94" t="str">
+    <row r="103" spans="1:66" s="1" customFormat="1" ht="18" hidden="1">
+      <c r="A103" s="4" t="str">
+        <f t="shared" si="40"/>
+        <v>1.27</v>
+      </c>
+      <c r="B103" s="93" t="s">
+        <v>96</v>
+      </c>
+      <c r="C103" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D103" s="5"/>
+      <c r="E103" s="6">
+        <v>46148</v>
+      </c>
+      <c r="F103" s="7">
+        <f t="shared" si="51"/>
+        <v>46154</v>
+      </c>
+      <c r="G103" s="8">
+        <v>7</v>
+      </c>
+      <c r="H103" s="9">
+        <v>0</v>
+      </c>
+      <c r="I103" s="10">
+        <f t="shared" si="52"/>
+        <v>5</v>
+      </c>
+      <c r="J103" s="11"/>
+      <c r="K103" s="4"/>
+      <c r="L103" s="4"/>
+      <c r="M103" s="4"/>
+      <c r="N103" s="4"/>
+      <c r="O103" s="4"/>
+      <c r="P103" s="4"/>
+      <c r="Q103" s="4"/>
+      <c r="R103" s="4"/>
+      <c r="S103" s="4"/>
+      <c r="T103" s="4"/>
+      <c r="U103" s="4"/>
+      <c r="V103" s="4"/>
+      <c r="W103" s="4"/>
+      <c r="X103" s="4"/>
+      <c r="Y103" s="4"/>
+      <c r="Z103" s="4"/>
+      <c r="AA103" s="4"/>
+      <c r="AB103" s="4"/>
+      <c r="AC103" s="4"/>
+      <c r="AD103" s="4"/>
+      <c r="AE103" s="4"/>
+      <c r="AF103" s="4"/>
+      <c r="AG103" s="4"/>
+      <c r="AH103" s="4"/>
+      <c r="AI103" s="4"/>
+      <c r="AJ103" s="4"/>
+      <c r="AK103" s="4"/>
+      <c r="AL103" s="4"/>
+      <c r="AM103" s="4"/>
+      <c r="AN103" s="4"/>
+      <c r="AO103" s="4"/>
+      <c r="AP103" s="4"/>
+      <c r="AQ103" s="4"/>
+      <c r="AR103" s="4"/>
+      <c r="AS103" s="4"/>
+      <c r="AT103" s="4"/>
+      <c r="AU103" s="4"/>
+      <c r="AV103" s="4"/>
+      <c r="AW103" s="4"/>
+      <c r="AX103" s="4"/>
+      <c r="AY103" s="4"/>
+      <c r="AZ103" s="4"/>
+      <c r="BA103" s="4"/>
+      <c r="BB103" s="4"/>
+      <c r="BC103" s="4"/>
+      <c r="BD103" s="4"/>
+      <c r="BE103" s="4"/>
+      <c r="BF103" s="4"/>
+      <c r="BG103" s="4"/>
+      <c r="BH103" s="4"/>
+      <c r="BI103" s="4"/>
+      <c r="BJ103" s="4"/>
+      <c r="BK103" s="4"/>
+      <c r="BL103" s="4"/>
+      <c r="BM103" s="4"/>
+      <c r="BN103" s="4"/>
+    </row>
+    <row r="104" spans="1:66" s="55" customFormat="1" ht="18" hidden="1">
+      <c r="A104" s="94" t="str">
         <f>IF(ISERROR(VALUE(SUBSTITUTE(prevWBS,".",""))),"1",IF(ISERROR(FIND("`",SUBSTITUTE(prevWBS,".","`",1))),TEXT(VALUE(prevWBS)+1,"#"),TEXT(VALUE(LEFT(prevWBS,FIND("`",SUBSTITUTE(prevWBS,".","`",1))-1))+1,"#")))</f>
         <v>2</v>
       </c>
-      <c r="B103" s="95" t="s">
+      <c r="B104" s="95" t="s">
         <v>97</v>
       </c>
-      <c r="D103" s="96"/>
-      <c r="E103" s="97"/>
-      <c r="F103" s="97" t="str">
-        <f t="shared" si="43"/>
+      <c r="D104" s="96"/>
+      <c r="E104" s="97"/>
+      <c r="F104" s="97" t="str">
+        <f t="shared" si="47"/>
         <v xml:space="preserve"> - </v>
       </c>
-      <c r="G103" s="98"/>
-      <c r="H103" s="99"/>
-      <c r="I103" s="100" t="str">
-        <f t="shared" si="44"/>
+      <c r="G104" s="98"/>
+      <c r="H104" s="99"/>
+      <c r="I104" s="100" t="str">
+        <f t="shared" si="48"/>
         <v xml:space="preserve"> - </v>
       </c>
-      <c r="J103" s="101"/>
-      <c r="K103" s="102"/>
-      <c r="L103" s="102"/>
-      <c r="M103" s="102"/>
-      <c r="N103" s="102"/>
-      <c r="O103" s="102"/>
-      <c r="P103" s="102"/>
-      <c r="Q103" s="102"/>
-      <c r="R103" s="102"/>
-      <c r="S103" s="102"/>
-      <c r="T103" s="102"/>
-      <c r="U103" s="102"/>
-      <c r="V103" s="102"/>
-      <c r="W103" s="102"/>
-      <c r="X103" s="102"/>
-      <c r="Y103" s="102"/>
-      <c r="Z103" s="102"/>
-      <c r="AA103" s="102"/>
-      <c r="AB103" s="102"/>
-      <c r="AC103" s="102"/>
-      <c r="AD103" s="102"/>
-      <c r="AE103" s="102"/>
-      <c r="AF103" s="102"/>
-      <c r="AG103" s="102"/>
-      <c r="AH103" s="102"/>
-      <c r="AI103" s="102"/>
-      <c r="AJ103" s="102"/>
-      <c r="AK103" s="102"/>
-      <c r="AL103" s="102"/>
-      <c r="AM103" s="102"/>
-      <c r="AN103" s="102"/>
-      <c r="AO103" s="102"/>
-      <c r="AP103" s="102"/>
-      <c r="AQ103" s="102"/>
-      <c r="AR103" s="102"/>
-      <c r="AS103" s="102"/>
-      <c r="AT103" s="102"/>
-      <c r="AU103" s="102"/>
-      <c r="AV103" s="102"/>
-      <c r="AW103" s="102"/>
-      <c r="AX103" s="102"/>
-      <c r="AY103" s="102"/>
-      <c r="AZ103" s="102"/>
-      <c r="BA103" s="102"/>
-      <c r="BB103" s="102"/>
-      <c r="BC103" s="102"/>
-      <c r="BD103" s="102"/>
-      <c r="BE103" s="102"/>
-      <c r="BF103" s="102"/>
-      <c r="BG103" s="102"/>
-      <c r="BH103" s="102"/>
-      <c r="BI103" s="102"/>
-      <c r="BJ103" s="102"/>
-      <c r="BK103" s="102"/>
-      <c r="BL103" s="102"/>
-      <c r="BM103" s="102"/>
-      <c r="BN103" s="102"/>
-    </row>
-    <row r="104" spans="1:66" s="1" customFormat="1" ht="18" hidden="1">
-      <c r="A104" s="4" t="str">
-        <f t="shared" si="36"/>
-        <v>2.1</v>
-      </c>
-      <c r="B104" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="C104" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="D104" s="5"/>
-      <c r="E104" s="6">
-        <v>46034</v>
-      </c>
-      <c r="F104" s="7">
-        <f t="shared" si="43"/>
-        <v>46038</v>
-      </c>
-      <c r="G104" s="8">
-        <v>5</v>
-      </c>
-      <c r="H104" s="9">
-        <v>0</v>
-      </c>
-      <c r="I104" s="10">
-        <f t="shared" si="44"/>
-        <v>5</v>
-      </c>
-      <c r="J104" s="11"/>
-      <c r="K104" s="4"/>
-      <c r="L104" s="4"/>
-      <c r="M104" s="4"/>
-      <c r="N104" s="4"/>
-      <c r="O104" s="4"/>
-      <c r="P104" s="4"/>
-      <c r="Q104" s="4"/>
-      <c r="R104" s="4"/>
-      <c r="S104" s="4"/>
-      <c r="T104" s="4"/>
-      <c r="U104" s="4"/>
-      <c r="V104" s="4"/>
-      <c r="W104" s="4"/>
-      <c r="X104" s="4"/>
-      <c r="Y104" s="4"/>
-      <c r="Z104" s="4"/>
-      <c r="AA104" s="4"/>
-      <c r="AB104" s="4"/>
-      <c r="AC104" s="4"/>
-      <c r="AD104" s="4"/>
-      <c r="AE104" s="4"/>
-      <c r="AF104" s="4"/>
-      <c r="AG104" s="4"/>
-      <c r="AH104" s="4"/>
-      <c r="AI104" s="4"/>
-      <c r="AJ104" s="4"/>
-      <c r="AK104" s="4"/>
-      <c r="AL104" s="4"/>
-      <c r="AM104" s="4"/>
-      <c r="AN104" s="4"/>
-      <c r="AO104" s="4"/>
-      <c r="AP104" s="4"/>
-      <c r="AQ104" s="4"/>
-      <c r="AR104" s="4"/>
-      <c r="AS104" s="4"/>
-      <c r="AT104" s="4"/>
-      <c r="AU104" s="4"/>
-      <c r="AV104" s="4"/>
-      <c r="AW104" s="4"/>
-      <c r="AX104" s="4"/>
-      <c r="AY104" s="4"/>
-      <c r="AZ104" s="4"/>
-      <c r="BA104" s="4"/>
-      <c r="BB104" s="4"/>
-      <c r="BC104" s="4"/>
-      <c r="BD104" s="4"/>
-      <c r="BE104" s="4"/>
-      <c r="BF104" s="4"/>
-      <c r="BG104" s="4"/>
-      <c r="BH104" s="4"/>
-      <c r="BI104" s="4"/>
-      <c r="BJ104" s="4"/>
-      <c r="BK104" s="4"/>
-      <c r="BL104" s="4"/>
-      <c r="BM104" s="4"/>
-      <c r="BN104" s="4"/>
+      <c r="J104" s="101"/>
+      <c r="K104" s="102"/>
+      <c r="L104" s="102"/>
+      <c r="M104" s="102"/>
+      <c r="N104" s="102"/>
+      <c r="O104" s="102"/>
+      <c r="P104" s="102"/>
+      <c r="Q104" s="102"/>
+      <c r="R104" s="102"/>
+      <c r="S104" s="102"/>
+      <c r="T104" s="102"/>
+      <c r="U104" s="102"/>
+      <c r="V104" s="102"/>
+      <c r="W104" s="102"/>
+      <c r="X104" s="102"/>
+      <c r="Y104" s="102"/>
+      <c r="Z104" s="102"/>
+      <c r="AA104" s="102"/>
+      <c r="AB104" s="102"/>
+      <c r="AC104" s="102"/>
+      <c r="AD104" s="102"/>
+      <c r="AE104" s="102"/>
+      <c r="AF104" s="102"/>
+      <c r="AG104" s="102"/>
+      <c r="AH104" s="102"/>
+      <c r="AI104" s="102"/>
+      <c r="AJ104" s="102"/>
+      <c r="AK104" s="102"/>
+      <c r="AL104" s="102"/>
+      <c r="AM104" s="102"/>
+      <c r="AN104" s="102"/>
+      <c r="AO104" s="102"/>
+      <c r="AP104" s="102"/>
+      <c r="AQ104" s="102"/>
+      <c r="AR104" s="102"/>
+      <c r="AS104" s="102"/>
+      <c r="AT104" s="102"/>
+      <c r="AU104" s="102"/>
+      <c r="AV104" s="102"/>
+      <c r="AW104" s="102"/>
+      <c r="AX104" s="102"/>
+      <c r="AY104" s="102"/>
+      <c r="AZ104" s="102"/>
+      <c r="BA104" s="102"/>
+      <c r="BB104" s="102"/>
+      <c r="BC104" s="102"/>
+      <c r="BD104" s="102"/>
+      <c r="BE104" s="102"/>
+      <c r="BF104" s="102"/>
+      <c r="BG104" s="102"/>
+      <c r="BH104" s="102"/>
+      <c r="BI104" s="102"/>
+      <c r="BJ104" s="102"/>
+      <c r="BK104" s="102"/>
+      <c r="BL104" s="102"/>
+      <c r="BM104" s="102"/>
+      <c r="BN104" s="102"/>
     </row>
     <row r="105" spans="1:66" s="1" customFormat="1" ht="18" hidden="1">
       <c r="A105" s="4" t="str">
-        <f t="shared" si="36"/>
-        <v>2.2</v>
+        <f t="shared" si="40"/>
+        <v>2.1</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="D105" s="5"/>
       <c r="E105" s="6">
-        <v>46023</v>
+        <v>46034</v>
       </c>
       <c r="F105" s="7">
-        <f t="shared" si="43"/>
-        <v>46032</v>
+        <f t="shared" si="47"/>
+        <v>46038</v>
       </c>
       <c r="G105" s="8">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="H105" s="9">
         <v>0</v>
       </c>
       <c r="I105" s="10">
-        <v>6</v>
+        <f t="shared" si="48"/>
+        <v>5</v>
       </c>
       <c r="J105" s="11"/>
       <c r="K105" s="4"/>
@@ -13087,33 +13129,33 @@
       <c r="BM105" s="4"/>
       <c r="BN105" s="4"/>
     </row>
-    <row r="106" spans="1:66" s="1" customFormat="1" ht="45" hidden="1" customHeight="1">
+    <row r="106" spans="1:66" s="1" customFormat="1" ht="18" hidden="1">
       <c r="A106" s="4" t="str">
-        <f t="shared" si="36"/>
-        <v>2.3</v>
+        <f t="shared" si="40"/>
+        <v>2.2</v>
       </c>
       <c r="B106" s="3" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>69</v>
+        <v>100</v>
       </c>
       <c r="D106" s="5"/>
       <c r="E106" s="6">
-        <v>46034</v>
+        <v>46023</v>
       </c>
       <c r="F106" s="7">
-        <f t="shared" si="43"/>
-        <v>46038</v>
+        <f t="shared" si="47"/>
+        <v>46032</v>
       </c>
       <c r="G106" s="8">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H106" s="9">
         <v>0</v>
       </c>
       <c r="I106" s="10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J106" s="11"/>
       <c r="K106" s="4"/>
@@ -13173,187 +13215,187 @@
       <c r="BM106" s="4"/>
       <c r="BN106" s="4"/>
     </row>
-    <row r="107" spans="1:66" s="55" customFormat="1" ht="18" hidden="1">
-      <c r="A107" s="94" t="str">
+    <row r="107" spans="1:66" s="1" customFormat="1" ht="45" hidden="1" customHeight="1">
+      <c r="A107" s="4" t="str">
+        <f t="shared" si="40"/>
+        <v>2.3</v>
+      </c>
+      <c r="B107" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="C107" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="D107" s="5"/>
+      <c r="E107" s="6">
+        <v>46034</v>
+      </c>
+      <c r="F107" s="7">
+        <f t="shared" si="47"/>
+        <v>46038</v>
+      </c>
+      <c r="G107" s="8">
+        <v>5</v>
+      </c>
+      <c r="H107" s="9">
+        <v>0</v>
+      </c>
+      <c r="I107" s="10">
+        <v>5</v>
+      </c>
+      <c r="J107" s="11"/>
+      <c r="K107" s="4"/>
+      <c r="L107" s="4"/>
+      <c r="M107" s="4"/>
+      <c r="N107" s="4"/>
+      <c r="O107" s="4"/>
+      <c r="P107" s="4"/>
+      <c r="Q107" s="4"/>
+      <c r="R107" s="4"/>
+      <c r="S107" s="4"/>
+      <c r="T107" s="4"/>
+      <c r="U107" s="4"/>
+      <c r="V107" s="4"/>
+      <c r="W107" s="4"/>
+      <c r="X107" s="4"/>
+      <c r="Y107" s="4"/>
+      <c r="Z107" s="4"/>
+      <c r="AA107" s="4"/>
+      <c r="AB107" s="4"/>
+      <c r="AC107" s="4"/>
+      <c r="AD107" s="4"/>
+      <c r="AE107" s="4"/>
+      <c r="AF107" s="4"/>
+      <c r="AG107" s="4"/>
+      <c r="AH107" s="4"/>
+      <c r="AI107" s="4"/>
+      <c r="AJ107" s="4"/>
+      <c r="AK107" s="4"/>
+      <c r="AL107" s="4"/>
+      <c r="AM107" s="4"/>
+      <c r="AN107" s="4"/>
+      <c r="AO107" s="4"/>
+      <c r="AP107" s="4"/>
+      <c r="AQ107" s="4"/>
+      <c r="AR107" s="4"/>
+      <c r="AS107" s="4"/>
+      <c r="AT107" s="4"/>
+      <c r="AU107" s="4"/>
+      <c r="AV107" s="4"/>
+      <c r="AW107" s="4"/>
+      <c r="AX107" s="4"/>
+      <c r="AY107" s="4"/>
+      <c r="AZ107" s="4"/>
+      <c r="BA107" s="4"/>
+      <c r="BB107" s="4"/>
+      <c r="BC107" s="4"/>
+      <c r="BD107" s="4"/>
+      <c r="BE107" s="4"/>
+      <c r="BF107" s="4"/>
+      <c r="BG107" s="4"/>
+      <c r="BH107" s="4"/>
+      <c r="BI107" s="4"/>
+      <c r="BJ107" s="4"/>
+      <c r="BK107" s="4"/>
+      <c r="BL107" s="4"/>
+      <c r="BM107" s="4"/>
+      <c r="BN107" s="4"/>
+    </row>
+    <row r="108" spans="1:66" s="55" customFormat="1" ht="18" hidden="1">
+      <c r="A108" s="94" t="str">
         <f>IF(ISERROR(VALUE(SUBSTITUTE(prevWBS,".",""))),"1",IF(ISERROR(FIND("`",SUBSTITUTE(prevWBS,".","`",1))),TEXT(VALUE(prevWBS)+1,"#"),TEXT(VALUE(LEFT(prevWBS,FIND("`",SUBSTITUTE(prevWBS,".","`",1))-1))+1,"#")))</f>
         <v>3</v>
       </c>
-      <c r="B107" s="95" t="s">
+      <c r="B108" s="95" t="s">
         <v>102</v>
       </c>
-      <c r="D107" s="96"/>
-      <c r="E107" s="97"/>
-      <c r="F107" s="97" t="str">
-        <f t="shared" ref="F107:F112" si="49">IF(ISBLANK(E107)," - ",IF(G107=0,E107,E107+G107-1))</f>
+      <c r="D108" s="96"/>
+      <c r="E108" s="97"/>
+      <c r="F108" s="97" t="str">
+        <f t="shared" ref="F108:F113" si="53">IF(ISBLANK(E108)," - ",IF(G108=0,E108,E108+G108-1))</f>
         <v xml:space="preserve"> - </v>
       </c>
-      <c r="G107" s="98"/>
-      <c r="H107" s="99"/>
-      <c r="I107" s="100" t="str">
-        <f t="shared" ref="I107" si="50">IF(OR(F107=0,E107=0)," - ",NETWORKDAYS(E107,F107))</f>
+      <c r="G108" s="98"/>
+      <c r="H108" s="99"/>
+      <c r="I108" s="100" t="str">
+        <f t="shared" ref="I108" si="54">IF(OR(F108=0,E108=0)," - ",NETWORKDAYS(E108,F108))</f>
         <v xml:space="preserve"> - </v>
       </c>
-      <c r="J107" s="101"/>
-      <c r="K107" s="102"/>
-      <c r="L107" s="102"/>
-      <c r="M107" s="102"/>
-      <c r="N107" s="102"/>
-      <c r="O107" s="102"/>
-      <c r="P107" s="102"/>
-      <c r="Q107" s="102"/>
-      <c r="R107" s="102"/>
-      <c r="S107" s="102"/>
-      <c r="T107" s="102"/>
-      <c r="U107" s="102"/>
-      <c r="V107" s="102"/>
-      <c r="W107" s="102"/>
-      <c r="X107" s="102"/>
-      <c r="Y107" s="102"/>
-      <c r="Z107" s="102"/>
-      <c r="AA107" s="102"/>
-      <c r="AB107" s="102"/>
-      <c r="AC107" s="102"/>
-      <c r="AD107" s="102"/>
-      <c r="AE107" s="102"/>
-      <c r="AF107" s="102"/>
-      <c r="AG107" s="102"/>
-      <c r="AH107" s="102"/>
-      <c r="AI107" s="102"/>
-      <c r="AJ107" s="102"/>
-      <c r="AK107" s="102"/>
-      <c r="AL107" s="102"/>
-      <c r="AM107" s="102"/>
-      <c r="AN107" s="102"/>
-      <c r="AO107" s="102"/>
-      <c r="AP107" s="102"/>
-      <c r="AQ107" s="102"/>
-      <c r="AR107" s="102"/>
-      <c r="AS107" s="102"/>
-      <c r="AT107" s="102"/>
-      <c r="AU107" s="102"/>
-      <c r="AV107" s="102"/>
-      <c r="AW107" s="102"/>
-      <c r="AX107" s="102"/>
-      <c r="AY107" s="102"/>
-      <c r="AZ107" s="102"/>
-      <c r="BA107" s="102"/>
-      <c r="BB107" s="102"/>
-      <c r="BC107" s="102"/>
-      <c r="BD107" s="102"/>
-      <c r="BE107" s="102"/>
-      <c r="BF107" s="102"/>
-      <c r="BG107" s="102"/>
-      <c r="BH107" s="102"/>
-      <c r="BI107" s="102"/>
-      <c r="BJ107" s="102"/>
-      <c r="BK107" s="102"/>
-      <c r="BL107" s="102"/>
-      <c r="BM107" s="102"/>
-      <c r="BN107" s="102"/>
-    </row>
-    <row r="108" spans="1:66" s="1" customFormat="1" ht="18" hidden="1">
-      <c r="A108" s="4" t="str">
-        <f t="shared" si="36"/>
-        <v>3.1</v>
-      </c>
-      <c r="B108" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="C108" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="D108" s="5"/>
-      <c r="E108" s="6">
-        <v>46041</v>
-      </c>
-      <c r="F108" s="7">
-        <f t="shared" si="49"/>
-        <v>46044</v>
-      </c>
-      <c r="G108" s="8">
-        <v>4</v>
-      </c>
-      <c r="H108" s="9">
-        <v>0</v>
-      </c>
-      <c r="I108" s="10">
-        <v>4</v>
-      </c>
-      <c r="J108" s="11"/>
-      <c r="K108" s="4"/>
-      <c r="L108" s="4"/>
-      <c r="M108" s="4"/>
-      <c r="N108" s="4"/>
-      <c r="O108" s="4"/>
-      <c r="P108" s="4"/>
-      <c r="Q108" s="4"/>
-      <c r="R108" s="4"/>
-      <c r="S108" s="4"/>
-      <c r="T108" s="4"/>
-      <c r="U108" s="4"/>
-      <c r="V108" s="4"/>
-      <c r="W108" s="4"/>
-      <c r="X108" s="4"/>
-      <c r="Y108" s="4"/>
-      <c r="Z108" s="4"/>
-      <c r="AA108" s="4"/>
-      <c r="AB108" s="4"/>
-      <c r="AC108" s="4"/>
-      <c r="AD108" s="4"/>
-      <c r="AE108" s="4"/>
-      <c r="AF108" s="4"/>
-      <c r="AG108" s="4"/>
-      <c r="AH108" s="4"/>
-      <c r="AI108" s="4"/>
-      <c r="AJ108" s="4"/>
-      <c r="AK108" s="4"/>
-      <c r="AL108" s="4"/>
-      <c r="AM108" s="4"/>
-      <c r="AN108" s="4"/>
-      <c r="AO108" s="4"/>
-      <c r="AP108" s="4"/>
-      <c r="AQ108" s="4"/>
-      <c r="AR108" s="4"/>
-      <c r="AS108" s="4"/>
-      <c r="AT108" s="4"/>
-      <c r="AU108" s="4"/>
-      <c r="AV108" s="4"/>
-      <c r="AW108" s="4"/>
-      <c r="AX108" s="4"/>
-      <c r="AY108" s="4"/>
-      <c r="AZ108" s="4"/>
-      <c r="BA108" s="4"/>
-      <c r="BB108" s="4"/>
-      <c r="BC108" s="4"/>
-      <c r="BD108" s="4"/>
-      <c r="BE108" s="4"/>
-      <c r="BF108" s="4"/>
-      <c r="BG108" s="4"/>
-      <c r="BH108" s="4"/>
-      <c r="BI108" s="4"/>
-      <c r="BJ108" s="4"/>
-      <c r="BK108" s="4"/>
-      <c r="BL108" s="4"/>
-      <c r="BM108" s="4"/>
-      <c r="BN108" s="4"/>
+      <c r="J108" s="101"/>
+      <c r="K108" s="102"/>
+      <c r="L108" s="102"/>
+      <c r="M108" s="102"/>
+      <c r="N108" s="102"/>
+      <c r="O108" s="102"/>
+      <c r="P108" s="102"/>
+      <c r="Q108" s="102"/>
+      <c r="R108" s="102"/>
+      <c r="S108" s="102"/>
+      <c r="T108" s="102"/>
+      <c r="U108" s="102"/>
+      <c r="V108" s="102"/>
+      <c r="W108" s="102"/>
+      <c r="X108" s="102"/>
+      <c r="Y108" s="102"/>
+      <c r="Z108" s="102"/>
+      <c r="AA108" s="102"/>
+      <c r="AB108" s="102"/>
+      <c r="AC108" s="102"/>
+      <c r="AD108" s="102"/>
+      <c r="AE108" s="102"/>
+      <c r="AF108" s="102"/>
+      <c r="AG108" s="102"/>
+      <c r="AH108" s="102"/>
+      <c r="AI108" s="102"/>
+      <c r="AJ108" s="102"/>
+      <c r="AK108" s="102"/>
+      <c r="AL108" s="102"/>
+      <c r="AM108" s="102"/>
+      <c r="AN108" s="102"/>
+      <c r="AO108" s="102"/>
+      <c r="AP108" s="102"/>
+      <c r="AQ108" s="102"/>
+      <c r="AR108" s="102"/>
+      <c r="AS108" s="102"/>
+      <c r="AT108" s="102"/>
+      <c r="AU108" s="102"/>
+      <c r="AV108" s="102"/>
+      <c r="AW108" s="102"/>
+      <c r="AX108" s="102"/>
+      <c r="AY108" s="102"/>
+      <c r="AZ108" s="102"/>
+      <c r="BA108" s="102"/>
+      <c r="BB108" s="102"/>
+      <c r="BC108" s="102"/>
+      <c r="BD108" s="102"/>
+      <c r="BE108" s="102"/>
+      <c r="BF108" s="102"/>
+      <c r="BG108" s="102"/>
+      <c r="BH108" s="102"/>
+      <c r="BI108" s="102"/>
+      <c r="BJ108" s="102"/>
+      <c r="BK108" s="102"/>
+      <c r="BL108" s="102"/>
+      <c r="BM108" s="102"/>
+      <c r="BN108" s="102"/>
     </row>
     <row r="109" spans="1:66" s="1" customFormat="1" ht="18" hidden="1">
       <c r="A109" s="4" t="str">
-        <f t="shared" si="36"/>
-        <v>3.2</v>
+        <f t="shared" si="40"/>
+        <v>3.1</v>
       </c>
       <c r="B109" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C109" s="1" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="D109" s="5"/>
       <c r="E109" s="6">
         <v>46041</v>
       </c>
       <c r="F109" s="7">
-        <f t="shared" si="49"/>
+        <f t="shared" si="53"/>
         <v>46044</v>
       </c>
       <c r="G109" s="8">
@@ -13425,25 +13467,25 @@
     </row>
     <row r="110" spans="1:66" s="1" customFormat="1" ht="18" hidden="1">
       <c r="A110" s="4" t="str">
-        <f t="shared" si="36"/>
-        <v>3.3</v>
+        <f t="shared" si="40"/>
+        <v>3.2</v>
       </c>
       <c r="B110" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>19</v>
+        <v>69</v>
       </c>
       <c r="D110" s="5"/>
       <c r="E110" s="6">
-        <v>46045</v>
+        <v>46041</v>
       </c>
       <c r="F110" s="7">
-        <f t="shared" si="49"/>
-        <v>46050</v>
+        <f t="shared" si="53"/>
+        <v>46044</v>
       </c>
       <c r="G110" s="8">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H110" s="9">
         <v>0</v>
@@ -13511,22 +13553,22 @@
     </row>
     <row r="111" spans="1:66" s="1" customFormat="1" ht="18" hidden="1">
       <c r="A111" s="4" t="str">
-        <f t="shared" si="36"/>
-        <v>3.4</v>
+        <f t="shared" si="40"/>
+        <v>3.3</v>
       </c>
       <c r="B111" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C111" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D111" s="5"/>
       <c r="E111" s="6">
-        <v>46051</v>
+        <v>46045</v>
       </c>
       <c r="F111" s="7">
-        <f t="shared" si="49"/>
-        <v>46056</v>
+        <f t="shared" si="53"/>
+        <v>46050</v>
       </c>
       <c r="G111" s="8">
         <v>6</v>
@@ -13597,22 +13639,22 @@
     </row>
     <row r="112" spans="1:66" s="1" customFormat="1" ht="18" hidden="1">
       <c r="A112" s="4" t="str">
-        <f t="shared" si="36"/>
-        <v>3.5</v>
+        <f t="shared" si="40"/>
+        <v>3.4</v>
       </c>
       <c r="B112" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="D112" s="5"/>
       <c r="E112" s="6">
-        <v>46045</v>
+        <v>46051</v>
       </c>
       <c r="F112" s="7">
-        <f t="shared" si="49"/>
-        <v>46050</v>
+        <f t="shared" si="53"/>
+        <v>46056</v>
       </c>
       <c r="G112" s="8">
         <v>6</v>
@@ -13681,183 +13723,259 @@
       <c r="BM112" s="4"/>
       <c r="BN112" s="4"/>
     </row>
-    <row r="113" spans="1:66" s="55" customFormat="1" ht="18" hidden="1">
-      <c r="A113" s="94" t="str">
+    <row r="113" spans="1:66" s="1" customFormat="1" ht="18" hidden="1">
+      <c r="A113" s="4" t="str">
+        <f t="shared" si="40"/>
+        <v>3.5</v>
+      </c>
+      <c r="B113" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="C113" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D113" s="5"/>
+      <c r="E113" s="6">
+        <v>46045</v>
+      </c>
+      <c r="F113" s="7">
+        <f t="shared" si="53"/>
+        <v>46050</v>
+      </c>
+      <c r="G113" s="8">
+        <v>6</v>
+      </c>
+      <c r="H113" s="9">
+        <v>0</v>
+      </c>
+      <c r="I113" s="10">
+        <v>4</v>
+      </c>
+      <c r="J113" s="11"/>
+      <c r="K113" s="4"/>
+      <c r="L113" s="4"/>
+      <c r="M113" s="4"/>
+      <c r="N113" s="4"/>
+      <c r="O113" s="4"/>
+      <c r="P113" s="4"/>
+      <c r="Q113" s="4"/>
+      <c r="R113" s="4"/>
+      <c r="S113" s="4"/>
+      <c r="T113" s="4"/>
+      <c r="U113" s="4"/>
+      <c r="V113" s="4"/>
+      <c r="W113" s="4"/>
+      <c r="X113" s="4"/>
+      <c r="Y113" s="4"/>
+      <c r="Z113" s="4"/>
+      <c r="AA113" s="4"/>
+      <c r="AB113" s="4"/>
+      <c r="AC113" s="4"/>
+      <c r="AD113" s="4"/>
+      <c r="AE113" s="4"/>
+      <c r="AF113" s="4"/>
+      <c r="AG113" s="4"/>
+      <c r="AH113" s="4"/>
+      <c r="AI113" s="4"/>
+      <c r="AJ113" s="4"/>
+      <c r="AK113" s="4"/>
+      <c r="AL113" s="4"/>
+      <c r="AM113" s="4"/>
+      <c r="AN113" s="4"/>
+      <c r="AO113" s="4"/>
+      <c r="AP113" s="4"/>
+      <c r="AQ113" s="4"/>
+      <c r="AR113" s="4"/>
+      <c r="AS113" s="4"/>
+      <c r="AT113" s="4"/>
+      <c r="AU113" s="4"/>
+      <c r="AV113" s="4"/>
+      <c r="AW113" s="4"/>
+      <c r="AX113" s="4"/>
+      <c r="AY113" s="4"/>
+      <c r="AZ113" s="4"/>
+      <c r="BA113" s="4"/>
+      <c r="BB113" s="4"/>
+      <c r="BC113" s="4"/>
+      <c r="BD113" s="4"/>
+      <c r="BE113" s="4"/>
+      <c r="BF113" s="4"/>
+      <c r="BG113" s="4"/>
+      <c r="BH113" s="4"/>
+      <c r="BI113" s="4"/>
+      <c r="BJ113" s="4"/>
+      <c r="BK113" s="4"/>
+      <c r="BL113" s="4"/>
+      <c r="BM113" s="4"/>
+      <c r="BN113" s="4"/>
+    </row>
+    <row r="114" spans="1:66" s="55" customFormat="1" ht="18" hidden="1">
+      <c r="A114" s="94" t="str">
         <f>IF(ISERROR(VALUE(SUBSTITUTE(prevWBS,".",""))),"1",IF(ISERROR(FIND("`",SUBSTITUTE(prevWBS,".","`",1))),TEXT(VALUE(prevWBS)+1,"#"),TEXT(VALUE(LEFT(prevWBS,FIND("`",SUBSTITUTE(prevWBS,".","`",1))-1))+1,"#")))</f>
         <v>4</v>
       </c>
-      <c r="B113" s="95" t="s">
+      <c r="B114" s="95" t="s">
         <v>108</v>
       </c>
-      <c r="D113" s="96"/>
-      <c r="E113" s="97"/>
-      <c r="F113" s="97" t="str">
-        <f t="shared" ref="F113:F114" si="51">IF(ISBLANK(E113)," - ",IF(G113=0,E113,E113+G113-1))</f>
+      <c r="D114" s="96"/>
+      <c r="E114" s="97"/>
+      <c r="F114" s="97" t="str">
+        <f t="shared" ref="F114:F115" si="55">IF(ISBLANK(E114)," - ",IF(G114=0,E114,E114+G114-1))</f>
         <v xml:space="preserve"> - </v>
       </c>
-      <c r="G113" s="98"/>
-      <c r="H113" s="99"/>
-      <c r="I113" s="100" t="str">
-        <f t="shared" ref="I113" si="52">IF(OR(F113=0,E113=0)," - ",NETWORKDAYS(E113,F113))</f>
+      <c r="G114" s="98"/>
+      <c r="H114" s="99"/>
+      <c r="I114" s="100" t="str">
+        <f t="shared" ref="I114" si="56">IF(OR(F114=0,E114=0)," - ",NETWORKDAYS(E114,F114))</f>
         <v xml:space="preserve"> - </v>
       </c>
-      <c r="J113" s="101"/>
-      <c r="K113" s="102"/>
-      <c r="L113" s="102"/>
-      <c r="M113" s="102"/>
-      <c r="N113" s="102"/>
-      <c r="O113" s="102"/>
-      <c r="P113" s="102"/>
-      <c r="Q113" s="102"/>
-      <c r="R113" s="102"/>
-      <c r="S113" s="102"/>
-      <c r="T113" s="102"/>
-      <c r="U113" s="102"/>
-      <c r="V113" s="102"/>
-      <c r="W113" s="102"/>
-      <c r="X113" s="102"/>
-      <c r="Y113" s="102"/>
-      <c r="Z113" s="102"/>
-      <c r="AA113" s="102"/>
-      <c r="AB113" s="102"/>
-      <c r="AC113" s="102"/>
-      <c r="AD113" s="102"/>
-      <c r="AE113" s="102"/>
-      <c r="AF113" s="102"/>
-      <c r="AG113" s="102"/>
-      <c r="AH113" s="102"/>
-      <c r="AI113" s="102"/>
-      <c r="AJ113" s="102"/>
-      <c r="AK113" s="102"/>
-      <c r="AL113" s="102"/>
-      <c r="AM113" s="102"/>
-      <c r="AN113" s="102"/>
-      <c r="AO113" s="102"/>
-      <c r="AP113" s="102"/>
-      <c r="AQ113" s="102"/>
-      <c r="AR113" s="102"/>
-      <c r="AS113" s="102"/>
-      <c r="AT113" s="102"/>
-      <c r="AU113" s="102"/>
-      <c r="AV113" s="102"/>
-      <c r="AW113" s="102"/>
-      <c r="AX113" s="102"/>
-      <c r="AY113" s="102"/>
-      <c r="AZ113" s="102"/>
-      <c r="BA113" s="102"/>
-      <c r="BB113" s="102"/>
-      <c r="BC113" s="102"/>
-      <c r="BD113" s="102"/>
-      <c r="BE113" s="102"/>
-      <c r="BF113" s="102"/>
-      <c r="BG113" s="102"/>
-      <c r="BH113" s="102"/>
-      <c r="BI113" s="102"/>
-      <c r="BJ113" s="102"/>
-      <c r="BK113" s="102"/>
-      <c r="BL113" s="102"/>
-      <c r="BM113" s="102"/>
-      <c r="BN113" s="102"/>
-    </row>
-    <row r="114" spans="1:66" s="1" customFormat="1" ht="18" hidden="1">
-      <c r="A114" s="4" t="str">
-        <f t="shared" si="36"/>
+      <c r="J114" s="101"/>
+      <c r="K114" s="102"/>
+      <c r="L114" s="102"/>
+      <c r="M114" s="102"/>
+      <c r="N114" s="102"/>
+      <c r="O114" s="102"/>
+      <c r="P114" s="102"/>
+      <c r="Q114" s="102"/>
+      <c r="R114" s="102"/>
+      <c r="S114" s="102"/>
+      <c r="T114" s="102"/>
+      <c r="U114" s="102"/>
+      <c r="V114" s="102"/>
+      <c r="W114" s="102"/>
+      <c r="X114" s="102"/>
+      <c r="Y114" s="102"/>
+      <c r="Z114" s="102"/>
+      <c r="AA114" s="102"/>
+      <c r="AB114" s="102"/>
+      <c r="AC114" s="102"/>
+      <c r="AD114" s="102"/>
+      <c r="AE114" s="102"/>
+      <c r="AF114" s="102"/>
+      <c r="AG114" s="102"/>
+      <c r="AH114" s="102"/>
+      <c r="AI114" s="102"/>
+      <c r="AJ114" s="102"/>
+      <c r="AK114" s="102"/>
+      <c r="AL114" s="102"/>
+      <c r="AM114" s="102"/>
+      <c r="AN114" s="102"/>
+      <c r="AO114" s="102"/>
+      <c r="AP114" s="102"/>
+      <c r="AQ114" s="102"/>
+      <c r="AR114" s="102"/>
+      <c r="AS114" s="102"/>
+      <c r="AT114" s="102"/>
+      <c r="AU114" s="102"/>
+      <c r="AV114" s="102"/>
+      <c r="AW114" s="102"/>
+      <c r="AX114" s="102"/>
+      <c r="AY114" s="102"/>
+      <c r="AZ114" s="102"/>
+      <c r="BA114" s="102"/>
+      <c r="BB114" s="102"/>
+      <c r="BC114" s="102"/>
+      <c r="BD114" s="102"/>
+      <c r="BE114" s="102"/>
+      <c r="BF114" s="102"/>
+      <c r="BG114" s="102"/>
+      <c r="BH114" s="102"/>
+      <c r="BI114" s="102"/>
+      <c r="BJ114" s="102"/>
+      <c r="BK114" s="102"/>
+      <c r="BL114" s="102"/>
+      <c r="BM114" s="102"/>
+      <c r="BN114" s="102"/>
+    </row>
+    <row r="115" spans="1:66" s="1" customFormat="1" ht="18" hidden="1">
+      <c r="A115" s="4" t="str">
+        <f t="shared" si="40"/>
         <v>4.1</v>
       </c>
-      <c r="B114" s="3" t="s">
+      <c r="B115" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="C114" s="1" t="s">
+      <c r="C115" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="D114" s="5"/>
-      <c r="E114" s="6">
+      <c r="D115" s="5"/>
+      <c r="E115" s="6">
         <v>46051</v>
       </c>
-      <c r="F114" s="7">
-        <f t="shared" si="51"/>
+      <c r="F115" s="7">
+        <f t="shared" si="55"/>
         <v>46056</v>
       </c>
-      <c r="G114" s="8">
+      <c r="G115" s="8">
         <v>6</v>
       </c>
-      <c r="H114" s="9">
+      <c r="H115" s="9">
         <v>0</v>
       </c>
-      <c r="I114" s="10">
+      <c r="I115" s="10">
         <v>4</v>
       </c>
-      <c r="J114" s="11"/>
-      <c r="K114" s="4"/>
-      <c r="L114" s="4"/>
-      <c r="M114" s="4"/>
-      <c r="N114" s="4"/>
-      <c r="O114" s="4"/>
-      <c r="P114" s="4"/>
-      <c r="Q114" s="4"/>
-      <c r="R114" s="4"/>
-      <c r="S114" s="4"/>
-      <c r="T114" s="4"/>
-      <c r="U114" s="4"/>
-      <c r="V114" s="4"/>
-      <c r="W114" s="4"/>
-      <c r="X114" s="4"/>
-      <c r="Y114" s="4"/>
-      <c r="Z114" s="4"/>
-      <c r="AA114" s="4"/>
-      <c r="AB114" s="4"/>
-      <c r="AC114" s="4"/>
-      <c r="AD114" s="4"/>
-      <c r="AE114" s="4"/>
-      <c r="AF114" s="4"/>
-      <c r="AG114" s="4"/>
-      <c r="AH114" s="4"/>
-      <c r="AI114" s="4"/>
-      <c r="AJ114" s="4"/>
-      <c r="AK114" s="4"/>
-      <c r="AL114" s="4"/>
-      <c r="AM114" s="4"/>
-      <c r="AN114" s="4"/>
-      <c r="AO114" s="4"/>
-      <c r="AP114" s="4"/>
-      <c r="AQ114" s="4"/>
-      <c r="AR114" s="4"/>
-      <c r="AS114" s="4"/>
-      <c r="AT114" s="4"/>
-      <c r="AU114" s="4"/>
-      <c r="AV114" s="4"/>
-      <c r="AW114" s="4"/>
-      <c r="AX114" s="4"/>
-      <c r="AY114" s="4"/>
-      <c r="AZ114" s="4"/>
-      <c r="BA114" s="4"/>
-      <c r="BB114" s="4"/>
-      <c r="BC114" s="4"/>
-      <c r="BD114" s="4"/>
-      <c r="BE114" s="4"/>
-      <c r="BF114" s="4"/>
-      <c r="BG114" s="4"/>
-      <c r="BH114" s="4"/>
-      <c r="BI114" s="4"/>
-      <c r="BJ114" s="4"/>
-      <c r="BK114" s="4"/>
-      <c r="BL114" s="4"/>
-      <c r="BM114" s="4"/>
-      <c r="BN114" s="4"/>
+      <c r="J115" s="11"/>
+      <c r="K115" s="4"/>
+      <c r="L115" s="4"/>
+      <c r="M115" s="4"/>
+      <c r="N115" s="4"/>
+      <c r="O115" s="4"/>
+      <c r="P115" s="4"/>
+      <c r="Q115" s="4"/>
+      <c r="R115" s="4"/>
+      <c r="S115" s="4"/>
+      <c r="T115" s="4"/>
+      <c r="U115" s="4"/>
+      <c r="V115" s="4"/>
+      <c r="W115" s="4"/>
+      <c r="X115" s="4"/>
+      <c r="Y115" s="4"/>
+      <c r="Z115" s="4"/>
+      <c r="AA115" s="4"/>
+      <c r="AB115" s="4"/>
+      <c r="AC115" s="4"/>
+      <c r="AD115" s="4"/>
+      <c r="AE115" s="4"/>
+      <c r="AF115" s="4"/>
+      <c r="AG115" s="4"/>
+      <c r="AH115" s="4"/>
+      <c r="AI115" s="4"/>
+      <c r="AJ115" s="4"/>
+      <c r="AK115" s="4"/>
+      <c r="AL115" s="4"/>
+      <c r="AM115" s="4"/>
+      <c r="AN115" s="4"/>
+      <c r="AO115" s="4"/>
+      <c r="AP115" s="4"/>
+      <c r="AQ115" s="4"/>
+      <c r="AR115" s="4"/>
+      <c r="AS115" s="4"/>
+      <c r="AT115" s="4"/>
+      <c r="AU115" s="4"/>
+      <c r="AV115" s="4"/>
+      <c r="AW115" s="4"/>
+      <c r="AX115" s="4"/>
+      <c r="AY115" s="4"/>
+      <c r="AZ115" s="4"/>
+      <c r="BA115" s="4"/>
+      <c r="BB115" s="4"/>
+      <c r="BC115" s="4"/>
+      <c r="BD115" s="4"/>
+      <c r="BE115" s="4"/>
+      <c r="BF115" s="4"/>
+      <c r="BG115" s="4"/>
+      <c r="BH115" s="4"/>
+      <c r="BI115" s="4"/>
+      <c r="BJ115" s="4"/>
+      <c r="BK115" s="4"/>
+      <c r="BL115" s="4"/>
+      <c r="BM115" s="4"/>
+      <c r="BN115" s="4"/>
     </row>
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertRows="0" deleteRows="0"/>
   <mergeCells count="19">
-    <mergeCell ref="K1:AE1"/>
-    <mergeCell ref="C4:E4"/>
-    <mergeCell ref="K4:Q4"/>
-    <mergeCell ref="R4:X4"/>
-    <mergeCell ref="Y4:AE4"/>
-    <mergeCell ref="AF4:AL4"/>
-    <mergeCell ref="AM4:AS4"/>
-    <mergeCell ref="AT4:AZ4"/>
-    <mergeCell ref="BA4:BG4"/>
-    <mergeCell ref="BH4:BN4"/>
     <mergeCell ref="AM5:AS5"/>
     <mergeCell ref="AT5:AZ5"/>
     <mergeCell ref="BA5:BG5"/>
@@ -13867,9 +13985,19 @@
     <mergeCell ref="R5:X5"/>
     <mergeCell ref="Y5:AE5"/>
     <mergeCell ref="AF5:AL5"/>
+    <mergeCell ref="AF4:AL4"/>
+    <mergeCell ref="AM4:AS4"/>
+    <mergeCell ref="AT4:AZ4"/>
+    <mergeCell ref="BA4:BG4"/>
+    <mergeCell ref="BH4:BN4"/>
+    <mergeCell ref="K1:AE1"/>
+    <mergeCell ref="C4:E4"/>
+    <mergeCell ref="K4:Q4"/>
+    <mergeCell ref="R4:X4"/>
+    <mergeCell ref="Y4:AE4"/>
   </mergeCells>
-  <conditionalFormatting sqref="H8:H10 H75:H80 H20:H31">
-    <cfRule type="dataBar" priority="266">
+  <conditionalFormatting sqref="H8:H10 H76:H81 H20:H31">
+    <cfRule type="dataBar" priority="270">
       <dataBar>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="1"/>
@@ -13883,7 +14011,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H11">
-    <cfRule type="dataBar" priority="153">
+    <cfRule type="dataBar" priority="157">
       <dataBar>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="1"/>
@@ -13897,7 +14025,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H12:H15">
-    <cfRule type="dataBar" priority="149">
+    <cfRule type="dataBar" priority="153">
       <dataBar>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="1"/>
@@ -13911,7 +14039,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H16:H17">
-    <cfRule type="dataBar" priority="145">
+    <cfRule type="dataBar" priority="149">
       <dataBar>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="1"/>
@@ -13925,7 +14053,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H18">
-    <cfRule type="dataBar" priority="97">
+    <cfRule type="dataBar" priority="101">
       <dataBar>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="1"/>
@@ -13939,7 +14067,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H19">
-    <cfRule type="dataBar" priority="93">
+    <cfRule type="dataBar" priority="97">
       <dataBar>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="1"/>
@@ -13953,7 +14081,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H32">
-    <cfRule type="dataBar" priority="88">
+    <cfRule type="dataBar" priority="92">
       <dataBar>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="1"/>
@@ -13967,7 +14095,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H33">
-    <cfRule type="dataBar" priority="133">
+    <cfRule type="dataBar" priority="137">
       <dataBar>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="1"/>
@@ -13981,7 +14109,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H34">
-    <cfRule type="dataBar" priority="129">
+    <cfRule type="dataBar" priority="133">
       <dataBar>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="1"/>
@@ -13995,7 +14123,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H35">
-    <cfRule type="dataBar" priority="125">
+    <cfRule type="dataBar" priority="129">
       <dataBar>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="1"/>
@@ -14009,7 +14137,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H36">
-    <cfRule type="dataBar" priority="121">
+    <cfRule type="dataBar" priority="125">
       <dataBar>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="1"/>
@@ -14023,7 +14151,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H37">
-    <cfRule type="dataBar" priority="117">
+    <cfRule type="dataBar" priority="121">
       <dataBar>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="1"/>
@@ -14037,7 +14165,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H38">
-    <cfRule type="dataBar" priority="109">
+    <cfRule type="dataBar" priority="113">
       <dataBar>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="1"/>
@@ -14051,7 +14179,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H39">
-    <cfRule type="dataBar" priority="105">
+    <cfRule type="dataBar" priority="109">
       <dataBar>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="1"/>
@@ -14064,8 +14192,8 @@
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H61:H74 H40:H59">
-    <cfRule type="dataBar" priority="101">
+  <conditionalFormatting sqref="H62:H75 H40:H44 H46:H60">
+    <cfRule type="dataBar" priority="105">
       <dataBar>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="1"/>
@@ -14078,8 +14206,8 @@
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H81:H85">
-    <cfRule type="dataBar" priority="253">
+  <conditionalFormatting sqref="H82:H86">
+    <cfRule type="dataBar" priority="257">
       <dataBar>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="1"/>
@@ -14092,8 +14220,8 @@
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H86:H88">
-    <cfRule type="dataBar" priority="249">
+  <conditionalFormatting sqref="H87:H89">
+    <cfRule type="dataBar" priority="253">
       <dataBar>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="1"/>
@@ -14106,8 +14234,8 @@
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H89">
-    <cfRule type="dataBar" priority="193">
+  <conditionalFormatting sqref="H90">
+    <cfRule type="dataBar" priority="197">
       <dataBar>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="1"/>
@@ -14120,8 +14248,8 @@
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H90">
-    <cfRule type="dataBar" priority="189">
+  <conditionalFormatting sqref="H91">
+    <cfRule type="dataBar" priority="193">
       <dataBar>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="1"/>
@@ -14134,8 +14262,8 @@
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H91:H95">
-    <cfRule type="dataBar" priority="245">
+  <conditionalFormatting sqref="H92:H96">
+    <cfRule type="dataBar" priority="249">
       <dataBar>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="1"/>
@@ -14148,8 +14276,8 @@
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H96:H97">
-    <cfRule type="dataBar" priority="241">
+  <conditionalFormatting sqref="H97:H98">
+    <cfRule type="dataBar" priority="245">
       <dataBar>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="1"/>
@@ -14162,8 +14290,8 @@
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H98">
-    <cfRule type="dataBar" priority="185">
+  <conditionalFormatting sqref="H99">
+    <cfRule type="dataBar" priority="189">
       <dataBar>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="1"/>
@@ -14176,8 +14304,8 @@
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H99">
-    <cfRule type="dataBar" priority="177">
+  <conditionalFormatting sqref="H100">
+    <cfRule type="dataBar" priority="181">
       <dataBar>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="1"/>
@@ -14190,8 +14318,8 @@
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H100">
-    <cfRule type="dataBar" priority="173">
+  <conditionalFormatting sqref="H101">
+    <cfRule type="dataBar" priority="177">
       <dataBar>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="1"/>
@@ -14204,8 +14332,8 @@
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H101">
-    <cfRule type="dataBar" priority="165">
+  <conditionalFormatting sqref="H102">
+    <cfRule type="dataBar" priority="169">
       <dataBar>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="1"/>
@@ -14218,8 +14346,8 @@
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H102">
-    <cfRule type="dataBar" priority="161">
+  <conditionalFormatting sqref="H103">
+    <cfRule type="dataBar" priority="165">
       <dataBar>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="1"/>
@@ -14232,8 +14360,8 @@
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H103">
-    <cfRule type="dataBar" priority="233">
+  <conditionalFormatting sqref="H104">
+    <cfRule type="dataBar" priority="237">
       <dataBar>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="1"/>
@@ -14246,8 +14374,8 @@
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H104:H106">
-    <cfRule type="dataBar" priority="229">
+  <conditionalFormatting sqref="H105:H107">
+    <cfRule type="dataBar" priority="233">
       <dataBar>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="1"/>
@@ -14260,8 +14388,8 @@
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H107">
-    <cfRule type="dataBar" priority="221">
+  <conditionalFormatting sqref="H108">
+    <cfRule type="dataBar" priority="225">
       <dataBar>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="1"/>
@@ -14274,8 +14402,8 @@
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H108:H112">
-    <cfRule type="dataBar" priority="213">
+  <conditionalFormatting sqref="H109:H113">
+    <cfRule type="dataBar" priority="217">
       <dataBar>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="1"/>
@@ -14288,8 +14416,8 @@
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H113">
-    <cfRule type="dataBar" priority="201">
+  <conditionalFormatting sqref="H114">
+    <cfRule type="dataBar" priority="205">
       <dataBar>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="1"/>
@@ -14302,8 +14430,8 @@
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H114">
-    <cfRule type="dataBar" priority="197">
+  <conditionalFormatting sqref="H115">
+    <cfRule type="dataBar" priority="201">
       <dataBar>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="1"/>
@@ -14317,43 +14445,62 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K6:BN7">
-    <cfRule type="expression" dxfId="9" priority="309">
+    <cfRule type="expression" dxfId="10" priority="313">
       <formula>K$6=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K6:BN59">
-    <cfRule type="expression" dxfId="8" priority="1">
+  <conditionalFormatting sqref="K6:BN44 K46:BN60">
+    <cfRule type="expression" dxfId="9" priority="5">
       <formula>K$6=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K8:BN59">
-    <cfRule type="expression" dxfId="7" priority="2">
+  <conditionalFormatting sqref="K8:BN60">
+    <cfRule type="expression" dxfId="8" priority="6">
       <formula>AND($E8&lt;=K$6,ROUNDDOWN(($F8-$E8+1)*$H8,0)+$E8-1&gt;=K$6)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="6" priority="3">
+    <cfRule type="expression" dxfId="7" priority="7">
       <formula>AND(NOT(ISBLANK($E8)),$E8&lt;=K$6,$F8&gt;=K$6)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K61:BN114">
-    <cfRule type="expression" dxfId="5" priority="94">
+  <conditionalFormatting sqref="K62:BN115">
+    <cfRule type="expression" dxfId="6" priority="98">
       <formula>K$6=TODAY()</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="4" priority="95">
-      <formula>AND($E61&lt;=K$6,ROUNDDOWN(($F61-$E61+1)*$H61,0)+$E61-1&gt;=K$6)</formula>
+    <cfRule type="expression" dxfId="5" priority="99">
+      <formula>AND($E62&lt;=K$6,ROUNDDOWN(($F62-$E62+1)*$H62,0)+$E62-1&gt;=K$6)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="3" priority="96">
-      <formula>AND(NOT(ISBLANK($E61)),$E61&lt;=K$6,$F61&gt;=K$6)</formula>
+    <cfRule type="expression" dxfId="4" priority="100">
+      <formula>AND(NOT(ISBLANK($E62)),$E62&lt;=K$6,$F62&gt;=K$6)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K45:BN45">
+    <cfRule type="expression" dxfId="3" priority="1">
+      <formula>K$6=TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H45">
+    <cfRule type="dataBar" priority="4">
+      <dataBar>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="1"/>
+        <color theme="0" tint="-0.34998626667073579"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{10FFD160-01F1-4462-B21C-F2F42D564CF6}</x14:id>
+        </ext>
+      </extLst>
     </cfRule>
   </conditionalFormatting>
   <dataValidations disablePrompts="1" count="1">
-    <dataValidation allowBlank="1" showInputMessage="1" promptTitle="Display Week" prompt="Enter the week number to display first in the Gantt Chart. The weeks are numbered starting from the week containing the Project Start Date." sqref="H4" xr:uid="{00000000-0002-0000-0000-000000000000}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" promptTitle="Display Week" prompt="Enter the week number to display first in the Gantt Chart. The weeks are numbered starting from the week containing the Project Start Date." sqref="H4"/>
   </dataValidations>
   <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.5" footer="0.25"/>
   <pageSetup scale="53" orientation="landscape"/>
   <headerFooter alignWithMargins="0"/>
   <ignoredErrors>
-    <ignoredError sqref="A75" formula="1"/>
-    <ignoredError sqref="E75 G75:H75 H77:H79" unlockedFormula="1"/>
+    <ignoredError sqref="A76" formula="1"/>
+    <ignoredError sqref="E76 G76:H76 H78:H80" unlockedFormula="1"/>
   </ignoredErrors>
   <drawing r:id="rId1"/>
   <legacyDrawing r:id="rId2"/>
@@ -14401,7 +14548,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>H8:H10 H75:H80 H20:H31</xm:sqref>
+          <xm:sqref>H8:H10 H76:H81 H20:H31</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="dataBar" id="{7D2FC776-74D9-4476-9780-84A43220E42F}">
@@ -14611,7 +14758,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>H61:H74 H40:H59</xm:sqref>
+          <xm:sqref>H62:H75 H40:H44 H46:H60</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="dataBar" id="{42371291-0D80-4E1E-9284-6142435A513E}">
@@ -14626,7 +14773,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>H81:H85</xm:sqref>
+          <xm:sqref>H82:H86</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="dataBar" id="{7E1F46DF-94D3-493F-8F62-1BBC80142C82}">
@@ -14641,7 +14788,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>H86:H88</xm:sqref>
+          <xm:sqref>H87:H89</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="dataBar" id="{777DE504-C53C-40AD-B156-FC11B711CC19}">
@@ -14656,7 +14803,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>H89</xm:sqref>
+          <xm:sqref>H90</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="dataBar" id="{8854B788-5316-4981-9484-0CC42B534E1C}">
@@ -14671,7 +14818,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>H90</xm:sqref>
+          <xm:sqref>H91</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="dataBar" id="{5FEB3D9F-6CC4-4AAB-BF86-C0BABBC52D23}">
@@ -14686,7 +14833,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>H91:H95</xm:sqref>
+          <xm:sqref>H92:H96</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="dataBar" id="{9707A22E-3CF9-4056-A7F5-2ACE12DF7B60}">
@@ -14701,7 +14848,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>H96:H97</xm:sqref>
+          <xm:sqref>H97:H98</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="dataBar" id="{BFF2043D-3049-4183-818C-8274C086AD0A}">
@@ -14716,7 +14863,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>H98</xm:sqref>
+          <xm:sqref>H99</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="dataBar" id="{91CCD22A-5C58-4215-A973-F4B3F7C835FA}">
@@ -14731,7 +14878,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>H99</xm:sqref>
+          <xm:sqref>H100</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="dataBar" id="{418697C2-E203-4579-B7B5-F2871E4F6A79}">
@@ -14746,7 +14893,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>H100</xm:sqref>
+          <xm:sqref>H101</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="dataBar" id="{6521E0B8-B658-4C8C-865E-50CD31104E82}">
@@ -14761,7 +14908,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>H101</xm:sqref>
+          <xm:sqref>H102</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="dataBar" id="{555D1C5D-931E-4A6E-AB33-FD88BB128578}">
@@ -14776,7 +14923,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>H102</xm:sqref>
+          <xm:sqref>H103</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="dataBar" id="{00C1BFB6-CDC4-4B2E-A26A-8F79EFBFF917}">
@@ -14791,7 +14938,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>H103</xm:sqref>
+          <xm:sqref>H104</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="dataBar" id="{3E5FA6A5-B6BA-4F76-B2BD-822452AB785A}">
@@ -14806,7 +14953,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>H104:H106</xm:sqref>
+          <xm:sqref>H105:H107</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="dataBar" id="{EDD923D3-8F13-49A6-A23E-B3CD0D8158C9}">
@@ -14821,7 +14968,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>H107</xm:sqref>
+          <xm:sqref>H108</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="dataBar" id="{9090F994-BE31-4869-9350-CC9DEA17195F}">
@@ -14836,7 +14983,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>H108:H112</xm:sqref>
+          <xm:sqref>H109:H113</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="dataBar" id="{A5B265BB-F427-401C-8347-B9525CF52D17}">
@@ -14851,7 +14998,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>H113</xm:sqref>
+          <xm:sqref>H114</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="dataBar" id="{58E687B7-55DC-490E-A8CB-7F5BA5CDB16F}">
@@ -14866,7 +15013,22 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>H114</xm:sqref>
+          <xm:sqref>H115</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{10FFD160-01F1-4462-B21C-F2F42D564CF6}">
+            <x14:dataBar minLength="0" maxLength="100" gradient="0">
+              <x14:cfvo type="num">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>1</xm:f>
+              </x14:cfvo>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>H45</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
@@ -14875,7 +15037,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -15050,9 +15212,9 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="C7" r:id="rId1" xr:uid="{00000000-0004-0000-0100-000000000000}"/>
-    <hyperlink ref="B46" r:id="rId2" tooltip="Go to Vertex42.com" xr:uid="{00000000-0004-0000-0100-000001000000}"/>
-    <hyperlink ref="C13" r:id="rId3" xr:uid="{00000000-0004-0000-0100-000002000000}"/>
+    <hyperlink ref="C7" r:id="rId1"/>
+    <hyperlink ref="B46" r:id="rId2" tooltip="Go to Vertex42.com"/>
+    <hyperlink ref="C13" r:id="rId3"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="93" orientation="portrait"/>
@@ -15061,7 +15223,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet5"/>
   <dimension ref="A1:C94"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="12.75"/>
@@ -15113,10 +15275,10 @@
       </c>
     </row>
     <row r="13" spans="1:3" ht="18">
-      <c r="A13" s="115" t="s">
+      <c r="A13" s="117" t="s">
         <v>148</v>
       </c>
-      <c r="B13" s="115"/>
+      <c r="B13" s="117"/>
     </row>
     <row r="15" spans="1:3" s="22" customFormat="1" ht="18">
       <c r="A15" s="30"/>
@@ -15177,10 +15339,10 @@
       <c r="B23" s="36"/>
     </row>
     <row r="24" spans="1:3" ht="18">
-      <c r="A24" s="115" t="s">
+      <c r="A24" s="117" t="s">
         <v>159</v>
       </c>
-      <c r="B24" s="115"/>
+      <c r="B24" s="117"/>
     </row>
     <row r="25" spans="1:3" ht="43.5">
       <c r="A25" s="33"/>
@@ -15253,10 +15415,10 @@
       <c r="B37" s="36"/>
     </row>
     <row r="38" spans="1:2" ht="18">
-      <c r="A38" s="115" t="s">
+      <c r="A38" s="117" t="s">
         <v>169</v>
       </c>
-      <c r="B38" s="115"/>
+      <c r="B38" s="117"/>
     </row>
     <row r="39" spans="1:2" ht="28.5">
       <c r="B39" s="31" t="s">
@@ -15287,10 +15449,10 @@
       </c>
     </row>
     <row r="49" spans="1:2" ht="18">
-      <c r="A49" s="115" t="s">
+      <c r="A49" s="117" t="s">
         <v>175</v>
       </c>
-      <c r="B49" s="115"/>
+      <c r="B49" s="117"/>
     </row>
     <row r="50" spans="1:2" ht="28.5">
       <c r="B50" s="31" t="s">
@@ -15385,10 +15547,10 @@
       <c r="B64" s="42"/>
     </row>
     <row r="65" spans="1:2" ht="18">
-      <c r="A65" s="115" t="s">
+      <c r="A65" s="117" t="s">
         <v>195</v>
       </c>
-      <c r="B65" s="115"/>
+      <c r="B65" s="117"/>
     </row>
     <row r="66" spans="1:2" ht="42.75">
       <c r="B66" s="31" t="s">
@@ -15396,10 +15558,10 @@
       </c>
     </row>
     <row r="68" spans="1:2" ht="18">
-      <c r="A68" s="115" t="s">
+      <c r="A68" s="117" t="s">
         <v>197</v>
       </c>
-      <c r="B68" s="115"/>
+      <c r="B68" s="117"/>
     </row>
     <row r="69" spans="1:2" ht="15">
       <c r="A69" s="43" t="s">
@@ -15562,9 +15724,9 @@
     <mergeCell ref="A65:B65"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="B9" r:id="rId1" xr:uid="{00000000-0004-0000-0200-000000000000}"/>
-    <hyperlink ref="A2" r:id="rId2" xr:uid="{00000000-0004-0000-0200-000001000000}"/>
-    <hyperlink ref="B36" r:id="rId3" xr:uid="{00000000-0004-0000-0200-000002000000}"/>
+    <hyperlink ref="B9" r:id="rId1"/>
+    <hyperlink ref="A2" r:id="rId2"/>
+    <hyperlink ref="B36" r:id="rId3"/>
   </hyperlinks>
   <pageMargins left="0.5" right="0.5" top="0.25" bottom="0.25" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait"/>
@@ -15575,7 +15737,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:C29"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="12.75"/>
@@ -15750,8 +15912,8 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B4" r:id="rId1" xr:uid="{00000000-0004-0000-0300-000000000000}"/>
-    <hyperlink ref="B19" r:id="rId2" xr:uid="{00000000-0004-0000-0300-000001000000}"/>
+    <hyperlink ref="B4" r:id="rId1"/>
+    <hyperlink ref="B19" r:id="rId2"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>
@@ -15760,7 +15922,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:M5"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75"/>
   <cols>
@@ -15768,21 +15930,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="37.5" customHeight="1">
-      <c r="A1" s="116" t="s">
+      <c r="A1" s="118" t="s">
         <v>238</v>
       </c>
-      <c r="B1" s="116"/>
-      <c r="C1" s="116"/>
-      <c r="D1" s="116"/>
-      <c r="E1" s="116"/>
-      <c r="F1" s="116"/>
-      <c r="G1" s="116"/>
-      <c r="H1" s="116"/>
-      <c r="I1" s="116"/>
-      <c r="J1" s="116"/>
-      <c r="K1" s="116"/>
-      <c r="L1" s="116"/>
-      <c r="M1" s="116"/>
+      <c r="B1" s="118"/>
+      <c r="C1" s="118"/>
+      <c r="D1" s="118"/>
+      <c r="E1" s="118"/>
+      <c r="F1" s="118"/>
+      <c r="G1" s="118"/>
+      <c r="H1" s="118"/>
+      <c r="I1" s="118"/>
+      <c r="J1" s="118"/>
+      <c r="K1" s="118"/>
+      <c r="L1" s="118"/>
+      <c r="M1" s="118"/>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" t="s">
@@ -15805,7 +15967,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:BN22"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75"/>
   <cols>
@@ -15862,7 +16024,7 @@
       </c>
       <c r="D13" s="5"/>
       <c r="E13" s="6">
-        <f>GanttChart!F58+1</f>
+        <f>GanttChart!F59+1</f>
         <v>46115</v>
       </c>
       <c r="F13" s="7">
@@ -15950,7 +16112,7 @@
       </c>
       <c r="D14" s="5"/>
       <c r="E14" s="6">
-        <f>GanttChart!F59+1</f>
+        <f>GanttChart!F60+1</f>
         <v>46119</v>
       </c>
       <c r="F14" s="7">
